--- a/templates/M2_L7.xlsx
+++ b/templates/M2_L7.xlsx
@@ -61,17 +61,17 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="007A8090"/>
+      <color rgb="00A3A8B4"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="007A8090"/>
+      <b val="1"/>
+      <color rgb="002F6FEB"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -95,12 +95,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E9EBEF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4F5F7"/>
+        <fgColor rgb="00EAF2FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -130,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -152,32 +147,50 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -253,6 +266,156 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5524500" cy="3048000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5543550" cy="9296400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5543550" cy="6172200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5543550" cy="3048000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5543550" cy="3048000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -544,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -655,74 +818,90 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>노란 머리글이 주로 쓰는 칸이에요. 나머지는 위 설명과 회색 '예시' 줄을 따라 필요할 때만 써요. 예시 줄(번호 칸이 '예시')은 문제로 나오지 않아요.</t>
+          <t>노란 머리글은 늘 쓰는 칸, 연회색 머리글은 필요할 때 쓰는 칸(보기·정답·해설·지시문·우리말)이에요. 거의 안 쓰는 칸(시간·세트·상태 등)은 오른쪽에 접어 두었어요(표 위 + 를 누르면 보여요).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>답을 여러 개 인정하려면 | 로 나눠요: [as|so]  ·  Tom is as tall as Jake.|Jake is as tall as Tom.</t>
+          <t>파란 '예시' 줄은 문제로 나오지 않아요. 예시 줄을 복사해 쓸 때는 번호 칸의 '예시'를 지우세요.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>답을 여러 개 인정하려면 | 로 나눠요: [as|so]  ·  Tom is as tall as Jake.|Jake is as tall as Tom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>문제는 단어 → 문법 탭 순서 → 각 탭의 줄 순서로 나와요.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>단어장과 문법 탭의 표 오른쪽에 '이렇게 나와요' 화면 예시(프로젝터 · 학생 폰)가 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>AI로 내 파일 만들기</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>1. AI(챗GPT·Gemini·Claude 등)에 이 파일과 내 자료(본문·단어·문법 문제)를 함께 올려요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>2. 아래 회색 칸의 부탁 글을 복사해 붙여 넣어요.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>1. AI(챗GPT·Gemini·Claude 등)에 이 파일과 내 자료(본문·단어·문법 문제)를 함께 올려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2. 아래 칸의 부탁 글을 복사해 붙여 넣어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
           <t>3. 받은 파일을 [엑셀 올리기]로 올리고, 미리보기에서 문제와 정답을 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="116" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="24" ht="116" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>첨부한 M2_L7.xlsx와 똑같은 형식으로, 첨부한 내 자료의 퀴즈 파일을 만들어 줘.
-- 탭 이름, 머리글, 탭 순서는 그대로 두고, 열을 더하거나 셀을 합치지 마.
-- 각 탭의 회색 '예시' 줄은 그대로 두고, 그 아래 7과 내용만 지우고 내 자료로 채워.
+- 탭 이름, 머리글, 탭 순서, 열 순서는 그대로 두고, 열을 더하거나 셀을 합치지 마.
+- 각 탭의 파란 '예시' 줄은 그대로 두고, 그 아래 7과 내용만 지우고 내 자료로 채워.
 - 안내 탭의 표시를 그대로 써: 고르기 (A / B), 쓰기 [답], 고치기 [틀린 말 → 고친 말](표시는 4곳까지), 배열 조각 / 조각(첫 조각도 소문자).
 - 한 줄에 한 문제. 여러 답은 | 로 나누고, 정답은 문장 속 표시와 꼭 맞게 써. 모르는 칸은 비워 둬.
 - 파일 이름은 M2_L8.xlsx처럼 학년_단원으로 해 줘.</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A20:B20"/>
+  <mergeCells count="11">
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A22:B22"/>
   </mergeCells>
@@ -741,1324 +920,1322 @@
   <cols>
     <col width="16" customWidth="1" style="8" min="1" max="1"/>
     <col width="18" customWidth="1" style="8" min="2" max="2"/>
-    <col width="7" customWidth="1" style="8" min="3" max="3"/>
-    <col width="16" customWidth="1" style="8" min="4" max="4"/>
-    <col width="40" customWidth="1" style="3" min="5" max="5"/>
-    <col width="32" customWidth="1" style="3" min="6" max="6"/>
-    <col width="9" customWidth="1" style="8" min="7" max="7"/>
-    <col width="12" customWidth="1" style="8" min="8" max="8"/>
-    <col width="10" customWidth="1" style="8" min="9" max="9"/>
-    <col width="8" customWidth="1" style="8" min="10" max="10"/>
-    <col width="10" customWidth="1" style="8" min="11" max="11"/>
+    <col width="26" customWidth="1" style="3" min="3" max="3"/>
+    <col width="14" customWidth="1" style="3" min="4" max="4"/>
+    <col width="6" customWidth="1" style="8" min="5" max="5"/>
+    <col width="16" customWidth="1" style="3" min="6" max="6"/>
+    <col hidden="1" outlineLevel="1" width="10" customWidth="1" style="9" min="7" max="11"/>
+    <col width="3" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>단어</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>뜻</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>예문</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>헷갈리는 단어</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>품사</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>헷갈리는 단어</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>예문</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>예문 뜻</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>단원</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>시간(초)</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
-        <is>
-          <t>단원</t>
-        </is>
-      </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>단어ID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>prefer</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>(더) 좋아하다</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>동</t>
         </is>
       </c>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="13" t="n"/>
-      <c r="G2" s="12" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J2" s="12" t="n"/>
-      <c r="K2" s="11" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H2" s="17" t="n"/>
+      <c r="I2" s="16" t="n"/>
+      <c r="J2" s="17" t="n"/>
+      <c r="K2" s="16" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>pair</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>한 켤레[쌍]</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="13" t="n"/>
-      <c r="G3" s="12" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="n"/>
-      <c r="K3" s="11" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="n"/>
+      <c r="I3" s="16" t="n"/>
+      <c r="J3" s="17" t="n"/>
+      <c r="K3" s="16" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>metal</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="13" t="n"/>
-      <c r="G4" s="12" t="n"/>
-      <c r="H4" s="11" t="n"/>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J4" s="12" t="n"/>
-      <c r="K4" s="11" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="n"/>
+      <c r="I4" s="16" t="n"/>
+      <c r="J4" s="17" t="n"/>
+      <c r="K4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>교환하다</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>동</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="11" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="n"/>
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="17" t="n"/>
+      <c r="K5" s="16" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>customer</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>손님, 고객</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="11" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="n"/>
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="16" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>clerk</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>점원, 직원</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="12" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="11" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>pencil case</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>필통</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="11" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="n"/>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="16" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>try on</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>(옷 등을) 입어 보다</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="11" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="17" t="n"/>
+      <c r="K9" s="16" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>mirror</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>거울</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="11" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="16" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>helpful</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>기꺼이 돕는</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>형</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="11" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="n"/>
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="17" t="n"/>
+      <c r="K11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>birthday</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>생일</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J12" s="12" t="n"/>
-      <c r="K12" s="11" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="n"/>
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="16" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>flea market</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>벼룩시장</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J13" s="12" t="n"/>
-      <c r="K13" s="11" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="n"/>
+      <c r="I13" s="16" t="n"/>
+      <c r="J13" s="17" t="n"/>
+      <c r="K13" s="16" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>for sale</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>팔려고 내놓은</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="11" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="n"/>
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="17" t="n"/>
+      <c r="K14" s="16" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>stand</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>가판대</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="11" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="n"/>
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="17" t="n"/>
+      <c r="K15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>economy</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>경제</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="11" t="n"/>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="11" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="n"/>
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="17" t="n"/>
+      <c r="K16" s="16" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>give away</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>무료로 주다</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="11" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="17" t="n"/>
+      <c r="K17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>secondhand</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>중고의</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>형</t>
         </is>
       </c>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="11" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="n"/>
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="17" t="n"/>
+      <c r="K18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>rental</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>임대, 대여</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J19" s="12" t="n"/>
-      <c r="K19" s="11" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="n"/>
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="17" t="n"/>
+      <c r="K19" s="16" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>rent</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>빌리다, 임차하다</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>동</t>
         </is>
       </c>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="11" t="n"/>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J20" s="12" t="n"/>
-      <c r="K20" s="11" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="n"/>
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="17" t="n"/>
+      <c r="K20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>lock</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>자물쇠</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J21" s="12" t="n"/>
-      <c r="K21" s="11" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="n"/>
+      <c r="I21" s="16" t="n"/>
+      <c r="J21" s="17" t="n"/>
+      <c r="K21" s="16" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>spend</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>(돈을) 쓰다</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>동</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="11" t="n"/>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="n"/>
-      <c r="K22" s="11" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="n"/>
+      <c r="I22" s="16" t="n"/>
+      <c r="J22" s="17" t="n"/>
+      <c r="K22" s="16" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>scan</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>스캔하다, 훑다</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>동</t>
         </is>
       </c>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J23" s="12" t="n"/>
-      <c r="K23" s="11" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="n"/>
+      <c r="I23" s="16" t="n"/>
+      <c r="J23" s="17" t="n"/>
+      <c r="K23" s="16" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>allow</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>허락하다, 가능하게 하다</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>동</t>
         </is>
       </c>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="11" t="n"/>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J24" s="12" t="n"/>
-      <c r="K24" s="11" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="n"/>
+      <c r="I24" s="16" t="n"/>
+      <c r="J24" s="17" t="n"/>
+      <c r="K24" s="16" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>easily</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>쉽게</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>부</t>
         </is>
       </c>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="11" t="n"/>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J25" s="12" t="n"/>
-      <c r="K25" s="11" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="n"/>
+      <c r="I25" s="16" t="n"/>
+      <c r="J25" s="17" t="n"/>
+      <c r="K25" s="16" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>free</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>무료의</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>형</t>
         </is>
       </c>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="11" t="n"/>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="11" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="16" t="n"/>
+      <c r="J26" s="17" t="n"/>
+      <c r="K26" s="16" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>instead of</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>~ 대신에</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="11" t="n"/>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J27" s="12" t="n"/>
-      <c r="K27" s="11" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="n"/>
+      <c r="I27" s="16" t="n"/>
+      <c r="J27" s="17" t="n"/>
+      <c r="K27" s="16" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>in good condition</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>상태가 좋은</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="11" t="n"/>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J28" s="12" t="n"/>
-      <c r="K28" s="11" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="17" t="n"/>
+      <c r="K28" s="16" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>head for</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>~로 향하다</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="11" t="n"/>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J29" s="12" t="n"/>
-      <c r="K29" s="11" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="16" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="16" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="11" t="n"/>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J30" s="12" t="n"/>
-      <c r="K30" s="11" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H30" s="17" t="n"/>
+      <c r="I30" s="16" t="n"/>
+      <c r="J30" s="17" t="n"/>
+      <c r="K30" s="16" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>wallet</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>지갑</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="12" t="n"/>
-      <c r="H31" s="11" t="n"/>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J31" s="12" t="n"/>
-      <c r="K31" s="11" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H31" s="17" t="n"/>
+      <c r="I31" s="16" t="n"/>
+      <c r="J31" s="17" t="n"/>
+      <c r="K31" s="16" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>현금</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="12" t="n"/>
-      <c r="H32" s="11" t="n"/>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J32" s="12" t="n"/>
-      <c r="K32" s="11" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="n"/>
+      <c r="I32" s="16" t="n"/>
+      <c r="J32" s="17" t="n"/>
+      <c r="K32" s="16" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>scratch</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>긁힌 자국</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="12" t="n"/>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J33" s="12" t="n"/>
-      <c r="K33" s="11" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="n"/>
+      <c r="I33" s="16" t="n"/>
+      <c r="J33" s="17" t="n"/>
+      <c r="K33" s="16" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>stay out</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>(밤에) 집 밖에 있다</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="12" t="n"/>
-      <c r="H34" s="11" t="n"/>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J34" s="12" t="n"/>
-      <c r="K34" s="11" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="n"/>
+      <c r="I34" s="16" t="n"/>
+      <c r="J34" s="17" t="n"/>
+      <c r="K34" s="16" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>water</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>(식물에) 물을 주다</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="15" t="inlineStr">
         <is>
           <t>동</t>
         </is>
       </c>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="12" t="n"/>
-      <c r="H35" s="11" t="n"/>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J35" s="12" t="n"/>
-      <c r="K35" s="11" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="n"/>
+      <c r="I35" s="16" t="n"/>
+      <c r="J35" s="17" t="n"/>
+      <c r="K35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>lake</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>호수</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="12" t="n"/>
-      <c r="H36" s="11" t="n"/>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J36" s="12" t="n"/>
-      <c r="K36" s="11" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="n"/>
+      <c r="I36" s="16" t="n"/>
+      <c r="J36" s="17" t="n"/>
+      <c r="K36" s="16" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>forget</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>잊다</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="15" t="inlineStr">
         <is>
           <t>동</t>
         </is>
       </c>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="12" t="n"/>
-      <c r="H37" s="11" t="n"/>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J37" s="12" t="n"/>
-      <c r="K37" s="11" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="16" t="n"/>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="16" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>scarf</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>목도리, 스카프</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="12" t="n"/>
-      <c r="H38" s="11" t="n"/>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J38" s="12" t="n"/>
-      <c r="K38" s="11" t="n"/>
+      <c r="F38" s="14" t="n"/>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="n"/>
+      <c r="I38" s="16" t="n"/>
+      <c r="J38" s="17" t="n"/>
+      <c r="K38" s="16" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>sneaker</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>운동화</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="12" t="n"/>
-      <c r="H39" s="11" t="n"/>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J39" s="12" t="n"/>
-      <c r="K39" s="11" t="n"/>
+      <c r="F39" s="14" t="n"/>
+      <c r="G39" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H39" s="17" t="n"/>
+      <c r="I39" s="16" t="n"/>
+      <c r="J39" s="17" t="n"/>
+      <c r="K39" s="16" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>boot</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>부츠, 장화</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="11" t="n"/>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J40" s="12" t="n"/>
-      <c r="K40" s="11" t="n"/>
+      <c r="F40" s="14" t="n"/>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="n"/>
+      <c r="I40" s="16" t="n"/>
+      <c r="J40" s="17" t="n"/>
+      <c r="K40" s="16" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>go well with</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>~와 잘 어울리다</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="11" t="n"/>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J41" s="12" t="n"/>
-      <c r="K41" s="11" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="14" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="14" t="n"/>
+      <c r="G41" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H41" s="17" t="n"/>
+      <c r="I41" s="16" t="n"/>
+      <c r="J41" s="17" t="n"/>
+      <c r="K41" s="16" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>gray</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>회색의</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>형</t>
         </is>
       </c>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="12" t="n"/>
-      <c r="H42" s="11" t="n"/>
-      <c r="I42" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J42" s="12" t="n"/>
-      <c r="K42" s="11" t="n"/>
+      <c r="F42" s="14" t="n"/>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="n"/>
+      <c r="I42" s="16" t="n"/>
+      <c r="J42" s="17" t="n"/>
+      <c r="K42" s="16" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>daughter</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>딸</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="14" t="n"/>
+      <c r="E43" s="15" t="inlineStr">
         <is>
           <t>명</t>
         </is>
       </c>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
-      <c r="G43" s="12" t="n"/>
-      <c r="H43" s="11" t="n"/>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J43" s="12" t="n"/>
-      <c r="K43" s="11" t="n"/>
+      <c r="F43" s="14" t="n"/>
+      <c r="G43" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H43" s="17" t="n"/>
+      <c r="I43" s="16" t="n"/>
+      <c r="J43" s="17" t="n"/>
+      <c r="K43" s="16" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>expensive</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>비싼</t>
         </is>
       </c>
-      <c r="C44" s="12" t="inlineStr">
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="14" t="n"/>
+      <c r="E44" s="15" t="inlineStr">
         <is>
           <t>형</t>
         </is>
       </c>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="12" t="n"/>
-      <c r="H44" s="11" t="n"/>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J44" s="12" t="n"/>
-      <c r="K44" s="11" t="n"/>
+      <c r="F44" s="14" t="n"/>
+      <c r="G44" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H44" s="17" t="n"/>
+      <c r="I44" s="16" t="n"/>
+      <c r="J44" s="17" t="n"/>
+      <c r="K44" s="16" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>wise</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>현명한, 지혜로운</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="15" t="inlineStr">
         <is>
           <t>형</t>
         </is>
       </c>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="12" t="n"/>
-      <c r="H45" s="11" t="n"/>
-      <c r="I45" s="11" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="J45" s="12" t="n"/>
-      <c r="K45" s="11" t="n"/>
+      <c r="F45" s="14" t="n"/>
+      <c r="G45" s="16" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="H45" s="17" t="n"/>
+      <c r="I45" s="16" t="n"/>
+      <c r="J45" s="17" t="n"/>
+      <c r="K45" s="16" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
       <formula1>"사용,검토,보관"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
+    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
       <formula1>5</formula1>
       <formula2>60</formula2>
     </dataValidation>
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="품사" error="명, 동, 형, 부, 대, 전, 접, 감, 구 중에서 고르세요." type="list">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="품사" error="명, 동, 형, 부, 대, 전, 접, 감, 구 중에서 고르세요." type="list">
       <formula1>"명,동,형,부,대,전,접,감,구"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2071,473 +2248,472 @@
   <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" style="8" min="1" max="1"/>
-    <col width="24" customWidth="1" style="3" min="2" max="2"/>
-    <col width="24" customWidth="1" style="3" min="3" max="3"/>
-    <col width="50" customWidth="1" style="3" min="4" max="4"/>
-    <col width="30" customWidth="1" style="3" min="5" max="5"/>
-    <col width="30" customWidth="1" style="3" min="6" max="6"/>
-    <col width="18" customWidth="1" style="3" min="7" max="7"/>
-    <col width="18" customWidth="1" style="3" min="8" max="8"/>
-    <col width="12" customWidth="1" style="8" min="9" max="9"/>
-    <col width="30" customWidth="1" style="3" min="10" max="10"/>
-    <col width="9" customWidth="1" style="8" min="11" max="11"/>
-    <col width="10" customWidth="1" style="8" min="12" max="12"/>
-    <col width="8" customWidth="1" style="8" min="13" max="13"/>
+    <col width="6" customWidth="1" style="9" min="1" max="1"/>
+    <col width="38" customWidth="1" style="3" min="2" max="2"/>
+    <col width="9" customWidth="1" style="8" min="3" max="3"/>
+    <col width="11" customWidth="1" style="3" min="4" max="4"/>
+    <col width="11" customWidth="1" style="3" min="5" max="5"/>
+    <col width="11" customWidth="1" style="3" min="6" max="6"/>
+    <col width="11" customWidth="1" style="3" min="7" max="7"/>
+    <col width="13" customWidth="1" style="3" min="8" max="8"/>
+    <col width="12" customWidth="1" style="3" min="9" max="9"/>
+    <col width="12" customWidth="1" style="3" min="10" max="10"/>
+    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="11" max="13"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
+          <t>문장</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>보기1</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>보기2</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>보기3</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>보기4</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>해설</t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
           <t>지시문</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>우리말</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>문장</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>보기1</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>보기2</t>
-        </is>
-      </c>
-      <c r="G1" s="10" t="inlineStr">
-        <is>
-          <t>보기3</t>
-        </is>
-      </c>
-      <c r="H1" s="10" t="inlineStr">
-        <is>
-          <t>보기4</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
-        <is>
-          <t>정답</t>
-        </is>
-      </c>
-      <c r="J1" s="10" t="inlineStr">
-        <is>
-          <t>해설</t>
-        </is>
-      </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>시간(초)</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="12" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
-      <c r="B2" s="15" t="n"/>
-      <c r="C2" s="15" t="n"/>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>I want (to go / going) home.</t>
         </is>
       </c>
-      <c r="E2" s="15" t="n"/>
-      <c r="F2" s="15" t="n"/>
-      <c r="G2" s="15" t="n"/>
-      <c r="H2" s="15" t="n"/>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
         <is>
           <t>to go</t>
         </is>
       </c>
-      <c r="J2" s="15" t="inlineStr">
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="inlineStr">
         <is>
           <t>want + to 동사원형</t>
         </is>
       </c>
-      <c r="K2" s="16" t="n"/>
-      <c r="L2" s="16" t="n"/>
-      <c r="M2" s="16" t="n"/>
+      <c r="I2" s="19" t="n"/>
+      <c r="J2" s="19" t="n"/>
+      <c r="K2" s="21" t="n"/>
+      <c r="L2" s="21" t="n"/>
+      <c r="M2" s="21" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="19" t="n"/>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>He make me laugh.</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>He makes me laugh.</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="n"/>
+      <c r="G3" s="19" t="n"/>
+      <c r="H3" s="19" t="inlineStr">
+        <is>
+          <t>주어가 3인칭 단수면 동사에 -s</t>
+        </is>
+      </c>
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>바른 문장을 고르세요.</t>
         </is>
       </c>
-      <c r="C3" s="15" t="n"/>
-      <c r="D3" s="15" t="n"/>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>He make me laugh.</t>
-        </is>
-      </c>
-      <c r="F3" s="15" t="inlineStr">
-        <is>
-          <t>He makes me laugh.</t>
-        </is>
-      </c>
-      <c r="G3" s="15" t="n"/>
-      <c r="H3" s="15" t="n"/>
-      <c r="I3" s="16" t="inlineStr">
+      <c r="J3" s="19" t="n"/>
+      <c r="K3" s="21" t="n"/>
+      <c r="L3" s="21" t="n"/>
+      <c r="M3" s="21" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>Bag A is as heavy as Bag B.</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+      <c r="F4" s="19" t="n"/>
+      <c r="G4" s="19" t="n"/>
+      <c r="H4" s="19" t="n"/>
+      <c r="I4" s="19" t="n"/>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>가방 A 3kg, 가방 B 3kg</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="n"/>
+      <c r="L4" s="21" t="n"/>
+      <c r="M4" s="21" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>The clerk let me (try / to try) on the sneakers.</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>try</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>let + 목적어 + 동사원형</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="17" t="n"/>
+      <c r="L5" s="16" t="n"/>
+      <c r="M5" s="17" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>My dad made me (water / watering) the plants every morning.</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>make + 목적어 + 동사원형</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="16" t="n"/>
+      <c r="M6" s="17" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>The teacher had us (exchange / exchanged) our notebooks.</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>have + 목적어 + 동사원형</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="n"/>
+      <c r="J7" s="14" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="17" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
-        <is>
-          <t>주어가 3인칭 단수면 동사에 -s</t>
-        </is>
-      </c>
-      <c r="K3" s="16" t="n"/>
-      <c r="L3" s="16" t="n"/>
-      <c r="M3" s="16" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>가방 A 3kg, 가방 B 3kg</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>Bag A is as heavy as Bag B.</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="n"/>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n"/>
-      <c r="I4" s="16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J4" s="15" t="n"/>
-      <c r="K4" s="16" t="n"/>
-      <c r="L4" s="16" t="n"/>
-      <c r="M4" s="16" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>The clerk let me (try / to try) on the sneakers.</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>try</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>My mom made me to clean my room.</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>My mom made me clean my room.</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>make + 목적어 + 동사원형 (to 없이)</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>어법상 바른 문장을 고르세요.</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="17" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>The flea market lets people (sell / to sell) their secondhand things.</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="14" t="n"/>
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>let + 목적어 + 동사원형</t>
         </is>
       </c>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="12" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>My dad made me (water / watering) the plants every morning.</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>water</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>make + 목적어 + 동사원형</t>
-        </is>
-      </c>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="12" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>The teacher had us (exchange / exchanged) our notebooks.</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
-        <is>
-          <t>have + 목적어 + 동사원형</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="12" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="I9" s="14" t="n"/>
+      <c r="J9" s="14" t="n"/>
+      <c r="K9" s="17" t="n"/>
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="17" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>This wallet is as (cheap / cheaper) as that one.</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>cheap</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>as + 원급 + as</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="n"/>
+      <c r="J10" s="14" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="16" t="n"/>
+      <c r="M10" s="17" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>My sneakers are as comfortable as yours.</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>My sneakers are as more comfortable as yours.</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>as ~ as 사이에는 원급</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>어법상 바른 문장을 고르세요.</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>My mom made me to clean my room.</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>My mom made me clean my room.</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
-        <is>
-          <t>make + 목적어 + 동사원형 (to 없이)</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="12" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>The flea market lets people (sell / to sell) their secondhand things.</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>sell</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>let + 목적어 + 동사원형</t>
-        </is>
-      </c>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="12" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>This wallet is as (cheap / cheaper) as that one.</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>cheap</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
-        <is>
-          <t>as + 원급 + as</t>
-        </is>
-      </c>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="11" t="n"/>
-      <c r="M10" s="12" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>어법상 바른 문장을 고르세요.</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>My sneakers are as comfortable as yours.</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>My sneakers are as more comfortable as yours.</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
-        <is>
-          <t>as ~ as 사이에는 원급</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="J11" s="14" t="n"/>
+      <c r="K11" s="17" t="n"/>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Mirror A is as expensive as Mirror B.</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="14" t="n"/>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>값이 다르니 as expensive as가 아니에요</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>다음 정보를 보고 문장이 맞으면 T, 틀리면 F를 고르세요.</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>거울 A: $20 / 거울 B: $30</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>Mirror A is as expensive as Mirror B.</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="13" t="n"/>
-      <c r="H12" s="13" t="n"/>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>값이 다르니 as expensive as가 아니에요</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="11" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="16" t="n"/>
+      <c r="M12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="A13" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>She sings as (beautiful / beautifully) as a singer.</t>
         </is>
       </c>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="13" t="n"/>
-      <c r="H13" s="13" t="n"/>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>beautifully</t>
         </is>
       </c>
-      <c r="J13" s="13" t="inlineStr">
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>sings를 꾸미니 부사 beautifully</t>
         </is>
       </c>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="I13" s="14" t="n"/>
+      <c r="J13" s="14" t="n"/>
+      <c r="K13" s="17" t="n"/>
+      <c r="L13" s="16" t="n"/>
+      <c r="M13" s="17" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -2550,6 +2726,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2562,279 +2739,278 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" style="8" min="1" max="1"/>
-    <col width="28" customWidth="1" style="3" min="2" max="2"/>
-    <col width="30" customWidth="1" style="3" min="3" max="3"/>
-    <col width="50" customWidth="1" style="3" min="4" max="4"/>
-    <col width="30" customWidth="1" style="3" min="5" max="5"/>
-    <col width="30" customWidth="1" style="3" min="6" max="6"/>
-    <col width="9" customWidth="1" style="8" min="7" max="7"/>
-    <col width="10" customWidth="1" style="8" min="8" max="8"/>
-    <col width="8" customWidth="1" style="8" min="9" max="9"/>
+    <col width="6" customWidth="1" style="9" min="1" max="1"/>
+    <col width="40" customWidth="1" style="3" min="2" max="2"/>
+    <col width="18" customWidth="1" style="3" min="3" max="3"/>
+    <col width="16" customWidth="1" style="3" min="4" max="4"/>
+    <col width="14" customWidth="1" style="3" min="5" max="5"/>
+    <col width="14" customWidth="1" style="3" min="6" max="6"/>
+    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="7" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
+          <t>문장</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>우리말</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>해설</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
           <t>지시문</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>우리말</t>
-        </is>
-      </c>
-      <c r="D1" s="9" t="inlineStr">
-        <is>
-          <t>문장</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>정답</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>해설</t>
-        </is>
-      </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>시간(초)</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
-      <c r="B2" s="15" t="n"/>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>He [doesn't] like milk.</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>그는 우유를 좋아하지 않는다.</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>He [doesn't] like milk.</t>
-        </is>
-      </c>
-      <c r="E2" s="15" t="n"/>
-      <c r="F2" s="15" t="n"/>
-      <c r="G2" s="16" t="n"/>
-      <c r="H2" s="16" t="n"/>
-      <c r="I2" s="16" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="21" t="n"/>
+      <c r="H2" s="21" t="n"/>
+      <c r="I2" s="21" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>I like cats. I like dogs.</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>I like cats and dogs.|I like dogs and cats.</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="n"/>
+      <c r="E3" s="19" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>and로 한 문장을 만드세요.</t>
         </is>
       </c>
-      <c r="C3" s="15" t="n"/>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>I like cats. I like dogs.</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>I like cats and dogs.|I like dogs and cats.</t>
-        </is>
-      </c>
-      <c r="F3" s="15" t="n"/>
-      <c r="G3" s="16" t="n"/>
-      <c r="H3" s="16" t="n"/>
-      <c r="I3" s="16" t="n"/>
+      <c r="G3" s="21" t="n"/>
+      <c r="H3" s="21" t="n"/>
+      <c r="I3" s="21" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="A4" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>My mom didn’t let me [stay out] late last night. (stay out)</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>let + 목적어 + 동사원형</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>괄호 안의 말을 알맞은 형태로 바꿔 빈칸에 쓰세요.</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>My mom didn’t let me [stay out] late last night. (stay out)</t>
-        </is>
-      </c>
-      <c r="E4" s="17" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="G4" s="17" t="n"/>
+      <c r="H4" s="16" t="n"/>
+      <c r="I4" s="17" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>The long line made the customers [wait] for an hour. (wait)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>make + 목적어 + 동사원형</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>괄호 안의 말을 알맞은 형태로 바꿔 빈칸에 쓰세요.</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="n"/>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="17" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>The clerk [let] me [exchange] the wallet.</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>그 점원은 내가 지갑을 교환하게 해 주었다.</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>let + 목적어 + 동사원형</t>
         </is>
       </c>
-      <c r="G4" s="12" t="n"/>
-      <c r="H4" s="11" t="n"/>
-      <c r="I4" s="12" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>괄호 안의 말을 알맞은 형태로 바꿔 빈칸에 쓰세요.</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>The long line made the customers [wait] for an hour. (wait)</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>make + 목적어 + 동사원형</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="12" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>우리말과 같도록 빈칸에 알맞은 말을 쓰세요.</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>그 점원은 내가 지갑을 교환하게 해 주었다.</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>The clerk [let] me [exchange] the wallet.</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>let + 목적어 + 동사원형</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="12" t="n"/>
+      <c r="G6" s="17" t="n"/>
+      <c r="H6" s="16" t="n"/>
+      <c r="I6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="A7" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>This scarf is [not] [as|so] expensive [as] that cap.</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>이 스카프는 저 모자만큼 비싸지 않다.</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>not as(so) + 원급 + as: ~만큼 …하지 않다</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>우리말과 같도록 빈칸에 알맞은 말을 쓰세요.</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>이 스카프는 저 모자만큼 비싸지 않다.</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>This scarf is [not] [as|so] expensive [as] that cap.</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>not as(so) + 원급 + as: ~만큼 …하지 않다</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="12" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Tom is 160 cm tall. Jake is 160 cm tall, too.</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Tom is as tall as Jake.|Jake is as tall as Tom.</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>키가 같으면 as tall as</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>두 문장을 as ~ as를 써서 한 문장으로 만드세요.</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>Tom is 160 cm tall. Jake is 160 cm tall, too.</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Tom is as tall as Jake.|Jake is as tall as Tom.</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>키가 같으면 as tall as</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="12" t="n"/>
+      <c r="G8" s="17" t="n"/>
+      <c r="H8" s="16" t="n"/>
+      <c r="I8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>My scarf is [as] warm [as] your jacket.</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>내 목도리는 네 재킷만큼 따뜻하다.</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>as + 원급 + as: ~만큼 …한</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>우리말과 같도록 빈칸에 알맞은 말을 쓰세요.</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>내 목도리는 네 재킷만큼 따뜻하다.</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>My scarf is [as] warm [as] your jacket.</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>as + 원급 + as: ~만큼 …한</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="12" t="n"/>
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="16" t="n"/>
+      <c r="I9" s="17" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -2847,6 +3023,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2859,127 +3036,126 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" style="8" min="1" max="1"/>
-    <col width="28" customWidth="1" style="3" min="2" max="2"/>
-    <col width="26" customWidth="1" style="3" min="3" max="3"/>
-    <col width="60" customWidth="1" style="3" min="4" max="4"/>
-    <col width="30" customWidth="1" style="3" min="5" max="5"/>
-    <col width="9" customWidth="1" style="8" min="6" max="6"/>
-    <col width="10" customWidth="1" style="8" min="7" max="7"/>
-    <col width="8" customWidth="1" style="8" min="8" max="8"/>
+    <col width="6" customWidth="1" style="9" min="1" max="1"/>
+    <col width="46" customWidth="1" style="3" min="2" max="2"/>
+    <col width="16" customWidth="1" style="3" min="3" max="3"/>
+    <col width="16" customWidth="1" style="3" min="4" max="4"/>
+    <col width="14" customWidth="1" style="3" min="5" max="5"/>
+    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="6" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
+          <t>문장</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>해설</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>우리말</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
           <t>지시문</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>우리말</t>
-        </is>
-      </c>
-      <c r="D1" s="9" t="inlineStr">
-        <is>
-          <t>문장</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>해설</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>시간(초)</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
-      <c r="B2" s="15" t="n"/>
-      <c r="C2" s="15" t="n"/>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>She [go → goes] to school every day.</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>주어가 3인칭 단수면 동사에 -s</t>
         </is>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16" t="n"/>
-      <c r="H2" s="16" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="21" t="n"/>
+      <c r="G2" s="21" t="n"/>
+      <c r="H2" s="21" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="A3" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>She had her son [to carry → carry] the boxes to the flea market.</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>have + 목적어 + 동사원형 (to 없이)</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>어법상 틀린 부분을 찾아 바르게 고치세요.</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>She had her son [to carry → carry] the boxes to the flea market.</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>have + 목적어 + 동사원형 (to 없이)</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="12" t="n"/>
+      <c r="F3" s="17" t="n"/>
+      <c r="G3" s="16" t="n"/>
+      <c r="H3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="A4" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>He runs as [fastly → fast] as his brother.</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>fast는 부사도 fast (fastly는 없는 말)</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>어법상 틀린 부분을 찾아 바르게 고치세요.</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>He runs as [fastly → fast] as his brother.</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>fast는 부사도 fast (fastly는 없는 말)</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="12" t="n"/>
+      <c r="F4" s="17" t="n"/>
+      <c r="G4" s="16" t="n"/>
+      <c r="H4" s="17" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -2992,6 +3168,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3004,151 +3181,150 @@
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" style="8" min="1" max="1"/>
-    <col width="28" customWidth="1" style="3" min="2" max="2"/>
-    <col width="32" customWidth="1" style="3" min="3" max="3"/>
-    <col width="56" customWidth="1" style="3" min="4" max="4"/>
-    <col width="30" customWidth="1" style="3" min="5" max="5"/>
-    <col width="9" customWidth="1" style="8" min="6" max="6"/>
-    <col width="10" customWidth="1" style="8" min="7" max="7"/>
-    <col width="8" customWidth="1" style="8" min="8" max="8"/>
+    <col width="6" customWidth="1" style="9" min="1" max="1"/>
+    <col width="42" customWidth="1" style="3" min="2" max="2"/>
+    <col width="22" customWidth="1" style="3" min="3" max="3"/>
+    <col width="14" customWidth="1" style="3" min="4" max="4"/>
+    <col width="14" customWidth="1" style="3" min="5" max="5"/>
+    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="6" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
+          <t>정답 (조각을 / 로)</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>우리말</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>해설</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
           <t>지시문</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>우리말</t>
-        </is>
-      </c>
-      <c r="D1" s="9" t="inlineStr">
-        <is>
-          <t>정답 (조각을 / 로)</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>해설</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>시간(초)</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
-      <c r="B2" s="15" t="n"/>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>my mom / makes / me / drink / milk / every day</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>엄마는 내가 매일 우유를 마시게 하신다.</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>my mom / makes / me / drink / milk / every day</t>
-        </is>
-      </c>
-      <c r="E2" s="15" t="n"/>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16" t="n"/>
-      <c r="H2" s="16" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="21" t="n"/>
+      <c r="G2" s="21" t="n"/>
+      <c r="H2" s="21" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="A3" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B3" s="13" t="n"/>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>the clerk / let / me / try on / the scarf</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>점원은 내가 그 스카프를 착용해 보게 해 주었다.</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>the clerk / let / me / try on / the scarf</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>let + 목적어 + 동사원형</t>
         </is>
       </c>
-      <c r="F3" s="12" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="12" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="17" t="n"/>
+      <c r="G3" s="16" t="n"/>
+      <c r="H3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="A4" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="B4" s="13" t="n"/>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>I / can / solve / the puzzle / as / easily / as / you</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>나는 너만큼 쉽게 그 퍼즐을 풀 수 있다.</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>I / can / solve / the puzzle / as / easily / as / you</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>as + 부사 원급 + as</t>
         </is>
       </c>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="12" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="17" t="n"/>
+      <c r="G4" s="16" t="n"/>
+      <c r="H4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="A5" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>these sneakers / are / not / as / expensive / as / those boots</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>이 운동화는 저 부츠만큼 비싸지 않다.</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>these sneakers / are / not / as / expensive / as / those boots</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>not as + 원급 + as</t>
         </is>
       </c>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="12" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="17" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -3161,6 +3337,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3170,110 +3347,462 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="8" min="1" max="1"/>
-    <col width="9" customWidth="1" style="8" min="2" max="2"/>
-    <col width="44" customWidth="1" style="3" min="3" max="3"/>
+    <col width="9" customWidth="1" style="8" min="1" max="1"/>
+    <col width="40" customWidth="1" style="3" min="2" max="2"/>
+    <col width="14" customWidth="1" style="3" min="3" max="3"/>
     <col width="14" customWidth="1" style="3" min="4" max="4"/>
     <col width="14" customWidth="1" style="3" min="5" max="5"/>
     <col width="14" customWidth="1" style="3" min="6" max="6"/>
-    <col width="14" customWidth="1" style="3" min="7" max="7"/>
-    <col width="10" customWidth="1" style="8" min="8" max="8"/>
-    <col width="36" customWidth="1" style="3" min="9" max="9"/>
-    <col width="24" customWidth="1" style="3" min="10" max="10"/>
-    <col width="24" customWidth="1" style="3" min="11" max="11"/>
-    <col width="24" customWidth="1" style="3" min="12" max="12"/>
-    <col width="24" customWidth="1" style="3" min="13" max="13"/>
-    <col width="9" customWidth="1" style="8" min="14" max="14"/>
-    <col width="12" customWidth="1" style="8" min="15" max="15"/>
-    <col width="8" customWidth="1" style="8" min="16" max="16"/>
+    <col width="9" customWidth="1" style="8" min="7" max="7"/>
+    <col width="28" customWidth="1" style="3" min="8" max="8"/>
+    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="9" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>유형</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>문제</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>보기1</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>보기2</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>보기3</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>보기4</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>해설</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>문항ID</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>유형</t>
-        </is>
-      </c>
-      <c r="C1" s="9" t="inlineStr">
-        <is>
-          <t>문제</t>
-        </is>
-      </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>보기1</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>보기2</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>보기3</t>
-        </is>
-      </c>
-      <c r="G1" s="10" t="inlineStr">
-        <is>
-          <t>보기4</t>
-        </is>
-      </c>
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>정답</t>
-        </is>
-      </c>
-      <c r="I1" s="10" t="inlineStr">
-        <is>
-          <t>해설</t>
-        </is>
-      </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>피드백1</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>피드백2</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>피드백3</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="12" t="inlineStr">
         <is>
           <t>피드백4</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="12" t="inlineStr">
         <is>
           <t>시간(초)</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="O1" s="12" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="P1" s="12" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="15" t="n"/>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="14" t="n"/>
+      <c r="I2" s="16" t="n"/>
+      <c r="J2" s="23" t="n"/>
+      <c r="K2" s="23" t="n"/>
+      <c r="L2" s="23" t="n"/>
+      <c r="M2" s="23" t="n"/>
+      <c r="N2" s="17" t="n"/>
+      <c r="O2" s="16" t="n"/>
+      <c r="P2" s="17" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="n"/>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="16" t="n"/>
+      <c r="J3" s="23" t="n"/>
+      <c r="K3" s="23" t="n"/>
+      <c r="L3" s="23" t="n"/>
+      <c r="M3" s="23" t="n"/>
+      <c r="N3" s="17" t="n"/>
+      <c r="O3" s="16" t="n"/>
+      <c r="P3" s="17" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="n"/>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="16" t="n"/>
+      <c r="J4" s="23" t="n"/>
+      <c r="K4" s="23" t="n"/>
+      <c r="L4" s="23" t="n"/>
+      <c r="M4" s="23" t="n"/>
+      <c r="N4" s="17" t="n"/>
+      <c r="O4" s="16" t="n"/>
+      <c r="P4" s="17" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="23" t="n"/>
+      <c r="K5" s="23" t="n"/>
+      <c r="L5" s="23" t="n"/>
+      <c r="M5" s="23" t="n"/>
+      <c r="N5" s="17" t="n"/>
+      <c r="O5" s="16" t="n"/>
+      <c r="P5" s="17" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n"/>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="23" t="n"/>
+      <c r="K6" s="23" t="n"/>
+      <c r="L6" s="23" t="n"/>
+      <c r="M6" s="23" t="n"/>
+      <c r="N6" s="17" t="n"/>
+      <c r="O6" s="16" t="n"/>
+      <c r="P6" s="17" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="14" t="n"/>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="23" t="n"/>
+      <c r="L7" s="23" t="n"/>
+      <c r="M7" s="23" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="16" t="n"/>
+      <c r="P7" s="17" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="23" t="n"/>
+      <c r="L8" s="23" t="n"/>
+      <c r="M8" s="23" t="n"/>
+      <c r="N8" s="17" t="n"/>
+      <c r="O8" s="16" t="n"/>
+      <c r="P8" s="17" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="14" t="n"/>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="23" t="n"/>
+      <c r="L9" s="23" t="n"/>
+      <c r="M9" s="23" t="n"/>
+      <c r="N9" s="17" t="n"/>
+      <c r="O9" s="16" t="n"/>
+      <c r="P9" s="17" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="14" t="n"/>
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="23" t="n"/>
+      <c r="L10" s="23" t="n"/>
+      <c r="M10" s="23" t="n"/>
+      <c r="N10" s="17" t="n"/>
+      <c r="O10" s="16" t="n"/>
+      <c r="P10" s="17" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="14" t="n"/>
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="23" t="n"/>
+      <c r="L11" s="23" t="n"/>
+      <c r="M11" s="23" t="n"/>
+      <c r="N11" s="17" t="n"/>
+      <c r="O11" s="16" t="n"/>
+      <c r="P11" s="17" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="14" t="n"/>
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="23" t="n"/>
+      <c r="L12" s="23" t="n"/>
+      <c r="M12" s="23" t="n"/>
+      <c r="N12" s="17" t="n"/>
+      <c r="O12" s="16" t="n"/>
+      <c r="P12" s="17" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="16" t="n"/>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="23" t="n"/>
+      <c r="L13" s="23" t="n"/>
+      <c r="M13" s="23" t="n"/>
+      <c r="N13" s="17" t="n"/>
+      <c r="O13" s="16" t="n"/>
+      <c r="P13" s="17" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="15" t="n"/>
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="23" t="n"/>
+      <c r="K14" s="23" t="n"/>
+      <c r="L14" s="23" t="n"/>
+      <c r="M14" s="23" t="n"/>
+      <c r="N14" s="17" t="n"/>
+      <c r="O14" s="16" t="n"/>
+      <c r="P14" s="17" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="23" t="n"/>
+      <c r="L15" s="23" t="n"/>
+      <c r="M15" s="23" t="n"/>
+      <c r="N15" s="17" t="n"/>
+      <c r="O15" s="16" t="n"/>
+      <c r="P15" s="17" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="23" t="n"/>
+      <c r="K16" s="23" t="n"/>
+      <c r="L16" s="23" t="n"/>
+      <c r="M16" s="23" t="n"/>
+      <c r="N16" s="17" t="n"/>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="17" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="23" t="n"/>
+      <c r="K17" s="23" t="n"/>
+      <c r="L17" s="23" t="n"/>
+      <c r="M17" s="23" t="n"/>
+      <c r="N17" s="17" t="n"/>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="17" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="23" t="n"/>
+      <c r="K18" s="23" t="n"/>
+      <c r="L18" s="23" t="n"/>
+      <c r="M18" s="23" t="n"/>
+      <c r="N18" s="17" t="n"/>
+      <c r="O18" s="16" t="n"/>
+      <c r="P18" s="17" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="23" t="n"/>
+      <c r="K19" s="23" t="n"/>
+      <c r="L19" s="23" t="n"/>
+      <c r="M19" s="23" t="n"/>
+      <c r="N19" s="17" t="n"/>
+      <c r="O19" s="16" t="n"/>
+      <c r="P19" s="17" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="23" t="n"/>
+      <c r="L20" s="23" t="n"/>
+      <c r="M20" s="23" t="n"/>
+      <c r="N20" s="17" t="n"/>
+      <c r="O20" s="16" t="n"/>
+      <c r="P20" s="17" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="16" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="23" t="n"/>
+      <c r="L21" s="23" t="n"/>
+      <c r="M21" s="23" t="n"/>
+      <c r="N21" s="17" t="n"/>
+      <c r="O21" s="16" t="n"/>
+      <c r="P21" s="17" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="P2:P500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
@@ -3283,7 +3812,7 @@
       <formula1>5</formula1>
       <formula2>60</formula2>
     </dataValidation>
-    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="유형" error="객관식, OX, 단답형 중에서 고르세요." type="list">
+    <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="유형" error="객관식, OX, 단답형 중에서 고르세요." type="list">
       <formula1>"객관식,OX,단답형"</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates/M2_L7.xlsx
+++ b/templates/M2_L7.xlsx
@@ -13,7 +13,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문법 쓰기" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문법 고치기" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문법 배열" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,12 +61,6 @@
     <font>
       <name val="맑은 고딕"/>
       <color rgb="00A3A8B4"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="002F6FEB"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -125,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -174,9 +167,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -188,9 +178,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -302,7 +289,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>14</col>
+      <col>13</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -332,7 +319,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
@@ -362,7 +349,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -392,7 +379,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -707,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -796,112 +783,100 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>문항 (선택)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>위에 없는 문제(반의어 등)를 직접 써요. 점수에는 들어가지 않는 보너스 문제예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>알아 두기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>노란 머리글은 늘 쓰는 칸, 연회색 머리글은 필요할 때 쓰는 칸(보기·정답·해설·지시문·우리말)이에요. 거의 안 쓰는 칸(시간·세트·상태 등)은 오른쪽에 접어 두었어요(표 위 + 를 누르면 보여요).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>노란 머리글은 늘 쓰는 칸, 연회색 머리글은 필요할 때 쓰는 칸(보기·정답·해설·지시문·우리말)이에요. 거의 안 쓰는 칸(시간·세트·상태 등)은 오른쪽에 접어 두었어요(표 위 + 를 누르면 보여요).</t>
+          <t>파란 줄은 예시라서 문제로 나오지 않아요. 예시 줄을 복사해 쓸 때는 내용을 고쳐 쓰면 문제가 돼요.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>파란 '예시' 줄은 문제로 나오지 않아요. 예시 줄을 복사해 쓸 때는 번호 칸의 '예시'를 지우세요.</t>
+          <t>답을 여러 개 인정하려면 | 로 나눠요: [as|so]  ·  Tom is as tall as Jake.|Jake is as tall as Tom.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>답을 여러 개 인정하려면 | 로 나눠요: [as|so]  ·  Tom is as tall as Jake.|Jake is as tall as Tom.</t>
+          <t>문제는 단어 → 문법 고르기 → 쓰기 → 고치기 → 배열 순서로 나오고, 같은 탭 안에서는 앱이 순서를 섞어요.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>문제는 단어 → 문법 탭 순서 → 각 탭의 줄 순서로 나와요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
           <t>단어장과 문법 탭의 표 오른쪽에 '이렇게 나와요' 화면 예시(프로젝터 · 학생 폰)가 있어요.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>AI로 내 파일 만들기</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>1. AI(챗GPT·Gemini·Claude 등)에 이 파일과 내 자료(본문·단어·문법 문제)를 함께 올려요.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>1. AI(챗GPT·Gemini·Claude 등)에 이 파일과 내 자료(본문·단어·문법 문제)를 함께 올려요.</t>
+          <t>2. 아래 칸의 부탁 글을 복사해 붙여 넣어요.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2. 아래 칸의 부탁 글을 복사해 붙여 넣어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
           <t>3. 받은 파일을 [엑셀 올리기]로 올리고, 미리보기에서 문제와 정답을 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="116" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="23" ht="116" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>첨부한 M2_L7.xlsx와 똑같은 형식으로, 첨부한 내 자료의 퀴즈 파일을 만들어 줘.
 - 탭 이름, 머리글, 탭 순서, 열 순서는 그대로 두고, 열을 더하거나 셀을 합치지 마.
-- 각 탭의 파란 '예시' 줄은 그대로 두고, 그 아래 7과 내용만 지우고 내 자료로 채워.
+- 각 탭 맨 위의 파란 예시 줄은 그대로 두고, 그 아래 7과 내용만 지우고 내 자료로 채워.
 - 안내 탭의 표시를 그대로 써: 고르기 (A / B), 쓰기 [답], 고치기 [틀린 말 → 고친 말](표시는 4곳까지), 배열 조각 / 조각(첫 조각도 소문자).
 - 한 줄에 한 문제. 여러 답은 | 로 나누고, 정답은 문장 속 표시와 꼭 맞게 써. 모르는 칸은 비워 둬.
 - 파일 이름은 M2_L8.xlsx처럼 학년_단원으로 해 줘.</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A22:B22"/>
   </mergeCells>
@@ -2245,85 +2220,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" style="9" min="1" max="1"/>
-    <col width="38" customWidth="1" style="3" min="2" max="2"/>
-    <col width="9" customWidth="1" style="8" min="3" max="3"/>
+    <col width="38" customWidth="1" style="3" min="1" max="1"/>
+    <col width="9" customWidth="1" style="8" min="2" max="2"/>
+    <col width="11" customWidth="1" style="3" min="3" max="3"/>
     <col width="11" customWidth="1" style="3" min="4" max="4"/>
     <col width="11" customWidth="1" style="3" min="5" max="5"/>
     <col width="11" customWidth="1" style="3" min="6" max="6"/>
-    <col width="11" customWidth="1" style="3" min="7" max="7"/>
-    <col width="13" customWidth="1" style="3" min="8" max="8"/>
+    <col width="13" customWidth="1" style="3" min="7" max="7"/>
+    <col width="12" customWidth="1" style="3" min="8" max="8"/>
     <col width="12" customWidth="1" style="3" min="9" max="9"/>
-    <col width="12" customWidth="1" style="3" min="10" max="10"/>
-    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="11" max="13"/>
-    <col width="3" customWidth="1" min="14" max="14"/>
+    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="10" max="12"/>
+    <col width="3" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>번호</t>
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>문장</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>문장</t>
-        </is>
-      </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
           <t>정답</t>
         </is>
       </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>보기1</t>
+        </is>
+      </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
-          <t>보기1</t>
+          <t>보기2</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
         <is>
-          <t>보기2</t>
+          <t>보기3</t>
         </is>
       </c>
       <c r="F1" s="11" t="inlineStr">
         <is>
-          <t>보기3</t>
+          <t>보기4</t>
         </is>
       </c>
       <c r="G1" s="11" t="inlineStr">
         <is>
-          <t>보기4</t>
+          <t>해설</t>
         </is>
       </c>
       <c r="H1" s="11" t="inlineStr">
         <is>
-          <t>해설</t>
+          <t>지시문</t>
         </is>
       </c>
       <c r="I1" s="11" t="inlineStr">
         <is>
-          <t>지시문</t>
-        </is>
-      </c>
-      <c r="J1" s="11" t="inlineStr">
-        <is>
           <t>우리말</t>
         </is>
       </c>
+      <c r="J1" s="12" t="inlineStr">
+        <is>
+          <t>시간(초)</t>
+        </is>
+      </c>
       <c r="K1" s="12" t="inlineStr">
         <is>
-          <t>시간(초)</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="L1" s="12" t="inlineStr">
-        <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="M1" s="12" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -2332,395 +2301,353 @@
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>예시</t>
+          <t>I want (to go / going) home.</t>
         </is>
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>I want (to go / going) home.</t>
-        </is>
-      </c>
-      <c r="C2" s="20" t="inlineStr">
-        <is>
           <t>to go</t>
         </is>
       </c>
-      <c r="D2" s="19" t="n"/>
-      <c r="E2" s="19" t="n"/>
-      <c r="F2" s="19" t="n"/>
-      <c r="G2" s="19" t="n"/>
-      <c r="H2" s="19" t="inlineStr">
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
+      <c r="F2" s="18" t="n"/>
+      <c r="G2" s="18" t="inlineStr">
         <is>
           <t>want + to 동사원형</t>
         </is>
       </c>
-      <c r="I2" s="19" t="n"/>
-      <c r="J2" s="19" t="n"/>
-      <c r="K2" s="21" t="n"/>
-      <c r="L2" s="21" t="n"/>
-      <c r="M2" s="21" t="n"/>
+      <c r="H2" s="18" t="n"/>
+      <c r="I2" s="18" t="n"/>
+      <c r="J2" s="20" t="n"/>
+      <c r="K2" s="20" t="n"/>
+      <c r="L2" s="20" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="n"/>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="A3" s="18" t="n"/>
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>He make me laugh.</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>He makes me laugh.</t>
         </is>
       </c>
-      <c r="F3" s="19" t="n"/>
-      <c r="G3" s="19" t="n"/>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="E3" s="18" t="n"/>
+      <c r="F3" s="18" t="n"/>
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>주어가 3인칭 단수면 동사에 -s</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>바른 문장을 고르세요.</t>
         </is>
       </c>
-      <c r="J3" s="19" t="n"/>
-      <c r="K3" s="21" t="n"/>
-      <c r="L3" s="21" t="n"/>
-      <c r="M3" s="21" t="n"/>
+      <c r="I3" s="18" t="n"/>
+      <c r="J3" s="20" t="n"/>
+      <c r="K3" s="20" t="n"/>
+      <c r="L3" s="20" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>예시</t>
+          <t>Bag A is as heavy as Bag B.</t>
         </is>
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>Bag A is as heavy as Bag B.</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="D4" s="19" t="n"/>
-      <c r="E4" s="19" t="n"/>
-      <c r="F4" s="19" t="n"/>
-      <c r="G4" s="19" t="n"/>
-      <c r="H4" s="19" t="n"/>
-      <c r="I4" s="19" t="n"/>
-      <c r="J4" s="19" t="inlineStr">
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="18" t="n"/>
+      <c r="F4" s="18" t="n"/>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n"/>
+      <c r="I4" s="18" t="inlineStr">
         <is>
           <t>가방 A 3kg, 가방 B 3kg</t>
         </is>
       </c>
-      <c r="K4" s="21" t="n"/>
-      <c r="L4" s="21" t="n"/>
-      <c r="M4" s="21" t="n"/>
+      <c r="J4" s="20" t="n"/>
+      <c r="K4" s="20" t="n"/>
+      <c r="L4" s="20" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>The clerk let me (try / to try) on the sneakers.</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>try</t>
         </is>
       </c>
+      <c r="C5" s="14" t="n"/>
       <c r="D5" s="14" t="n"/>
       <c r="E5" s="14" t="n"/>
       <c r="F5" s="14" t="n"/>
-      <c r="G5" s="14" t="n"/>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>let + 목적어 + 동사원형</t>
         </is>
       </c>
+      <c r="H5" s="14" t="n"/>
       <c r="I5" s="14" t="n"/>
-      <c r="J5" s="14" t="n"/>
-      <c r="K5" s="17" t="n"/>
-      <c r="L5" s="16" t="n"/>
-      <c r="M5" s="17" t="n"/>
+      <c r="J5" s="17" t="n"/>
+      <c r="K5" s="16" t="n"/>
+      <c r="L5" s="17" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>My dad made me (water / watering) the plants every morning.</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>water</t>
         </is>
       </c>
+      <c r="C6" s="14" t="n"/>
       <c r="D6" s="14" t="n"/>
       <c r="E6" s="14" t="n"/>
       <c r="F6" s="14" t="n"/>
-      <c r="G6" s="14" t="n"/>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>make + 목적어 + 동사원형</t>
         </is>
       </c>
+      <c r="H6" s="14" t="n"/>
       <c r="I6" s="14" t="n"/>
-      <c r="J6" s="14" t="n"/>
-      <c r="K6" s="17" t="n"/>
-      <c r="L6" s="16" t="n"/>
-      <c r="M6" s="17" t="n"/>
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>The teacher had us (exchange / exchanged) our notebooks.</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
+      <c r="C7" s="14" t="n"/>
       <c r="D7" s="14" t="n"/>
       <c r="E7" s="14" t="n"/>
       <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>have + 목적어 + 동사원형</t>
         </is>
       </c>
+      <c r="H7" s="14" t="n"/>
       <c r="I7" s="14" t="n"/>
-      <c r="J7" s="14" t="n"/>
-      <c r="K7" s="17" t="n"/>
-      <c r="L7" s="16" t="n"/>
-      <c r="M7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>My mom made me to clean my room.</t>
+        </is>
+      </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>My mom made me to clean my room.</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
           <t>My mom made me clean my room.</t>
         </is>
       </c>
+      <c r="E8" s="14" t="n"/>
       <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>make + 목적어 + 동사원형 (to 없이)</t>
+        </is>
+      </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>make + 목적어 + 동사원형 (to 없이)</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
           <t>어법상 바른 문장을 고르세요.</t>
         </is>
       </c>
-      <c r="J8" s="14" t="n"/>
-      <c r="K8" s="17" t="n"/>
-      <c r="L8" s="16" t="n"/>
-      <c r="M8" s="17" t="n"/>
+      <c r="I8" s="14" t="n"/>
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>The flea market lets people (sell / to sell) their secondhand things.</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>sell</t>
         </is>
       </c>
+      <c r="C9" s="14" t="n"/>
       <c r="D9" s="14" t="n"/>
       <c r="E9" s="14" t="n"/>
       <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>let + 목적어 + 동사원형</t>
         </is>
       </c>
+      <c r="H9" s="14" t="n"/>
       <c r="I9" s="14" t="n"/>
-      <c r="J9" s="14" t="n"/>
-      <c r="K9" s="17" t="n"/>
-      <c r="L9" s="16" t="n"/>
-      <c r="M9" s="17" t="n"/>
+      <c r="J9" s="17" t="n"/>
+      <c r="K9" s="16" t="n"/>
+      <c r="L9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>This wallet is as (cheap / cheaper) as that one.</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>cheap</t>
         </is>
       </c>
+      <c r="C10" s="14" t="n"/>
       <c r="D10" s="14" t="n"/>
       <c r="E10" s="14" t="n"/>
       <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>as + 원급 + as</t>
         </is>
       </c>
+      <c r="H10" s="14" t="n"/>
       <c r="I10" s="14" t="n"/>
-      <c r="J10" s="14" t="n"/>
-      <c r="K10" s="17" t="n"/>
-      <c r="L10" s="16" t="n"/>
-      <c r="M10" s="17" t="n"/>
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="16" t="n"/>
+      <c r="L10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>My sneakers are as comfortable as yours.</t>
+        </is>
+      </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>My sneakers are as comfortable as yours.</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
           <t>My sneakers are as more comfortable as yours.</t>
         </is>
       </c>
+      <c r="E11" s="14" t="n"/>
       <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>as ~ as 사이에는 원급</t>
+        </is>
+      </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>as ~ as 사이에는 원급</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
           <t>어법상 바른 문장을 고르세요.</t>
         </is>
       </c>
-      <c r="J11" s="14" t="n"/>
-      <c r="K11" s="17" t="n"/>
-      <c r="L11" s="16" t="n"/>
-      <c r="M11" s="17" t="n"/>
+      <c r="I11" s="14" t="n"/>
+      <c r="J11" s="17" t="n"/>
+      <c r="K11" s="16" t="n"/>
+      <c r="L11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Mirror A is as expensive as Mirror B.</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
+      <c r="C12" s="14" t="n"/>
       <c r="D12" s="14" t="n"/>
       <c r="E12" s="14" t="n"/>
       <c r="F12" s="14" t="n"/>
-      <c r="G12" s="14" t="n"/>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>값이 다르니 as expensive as가 아니에요</t>
+        </is>
+      </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>값이 다르니 as expensive as가 아니에요</t>
+          <t>다음 정보를 보고 문장이 맞으면 T, 틀리면 F를 고르세요.</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>다음 정보를 보고 문장이 맞으면 T, 틀리면 F를 고르세요.</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="inlineStr">
-        <is>
           <t>거울 A: $20 / 거울 B: $30</t>
         </is>
       </c>
-      <c r="K12" s="17" t="n"/>
-      <c r="L12" s="16" t="n"/>
-      <c r="M12" s="17" t="n"/>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="16" t="n"/>
+      <c r="L12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>She sings as (beautiful / beautifully) as a singer.</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>beautifully</t>
         </is>
       </c>
+      <c r="C13" s="14" t="n"/>
       <c r="D13" s="14" t="n"/>
       <c r="E13" s="14" t="n"/>
       <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>sings를 꾸미니 부사 beautifully</t>
         </is>
       </c>
+      <c r="H13" s="14" t="n"/>
       <c r="I13" s="14" t="n"/>
-      <c r="J13" s="14" t="n"/>
-      <c r="K13" s="17" t="n"/>
-      <c r="L13" s="16" t="n"/>
-      <c r="M13" s="17" t="n"/>
+      <c r="J13" s="17" t="n"/>
+      <c r="K13" s="16" t="n"/>
+      <c r="L13" s="17" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="M2:M500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
+    <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
       <formula1>"사용,검토,보관"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
+    <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
       <formula1>5</formula1>
       <formula2>60</formula2>
     </dataValidation>
@@ -2736,61 +2663,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" style="9" min="1" max="1"/>
-    <col width="40" customWidth="1" style="3" min="2" max="2"/>
-    <col width="18" customWidth="1" style="3" min="3" max="3"/>
-    <col width="16" customWidth="1" style="3" min="4" max="4"/>
+    <col width="40" customWidth="1" style="3" min="1" max="1"/>
+    <col width="18" customWidth="1" style="3" min="2" max="2"/>
+    <col width="16" customWidth="1" style="3" min="3" max="3"/>
+    <col width="14" customWidth="1" style="3" min="4" max="4"/>
     <col width="14" customWidth="1" style="3" min="5" max="5"/>
-    <col width="14" customWidth="1" style="3" min="6" max="6"/>
-    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="7" max="9"/>
-    <col width="3" customWidth="1" min="10" max="10"/>
+    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="6" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>문장</t>
         </is>
       </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
       <c r="C1" s="11" t="inlineStr">
         <is>
-          <t>정답</t>
+          <t>우리말</t>
         </is>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
-          <t>우리말</t>
+          <t>해설</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
         <is>
-          <t>해설</t>
-        </is>
-      </c>
-      <c r="F1" s="11" t="inlineStr">
-        <is>
           <t>지시문</t>
         </is>
       </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>시간(초)</t>
+        </is>
+      </c>
       <c r="G1" s="12" t="inlineStr">
         <is>
-          <t>시간(초)</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="H1" s="12" t="inlineStr">
-        <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -2799,225 +2720,197 @@
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="B2" s="19" t="inlineStr">
-        <is>
           <t>He [doesn't] like milk.</t>
         </is>
       </c>
-      <c r="C2" s="19" t="n"/>
-      <c r="D2" s="19" t="inlineStr">
+      <c r="B2" s="18" t="n"/>
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>그는 우유를 좋아하지 않는다.</t>
         </is>
       </c>
-      <c r="E2" s="19" t="n"/>
-      <c r="F2" s="19" t="n"/>
-      <c r="G2" s="21" t="n"/>
-      <c r="H2" s="21" t="n"/>
-      <c r="I2" s="21" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="20" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
           <t>I like cats. I like dogs.</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>I like cats and dogs.|I like dogs and cats.</t>
         </is>
       </c>
-      <c r="D3" s="19" t="n"/>
-      <c r="E3" s="19" t="n"/>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="C3" s="18" t="n"/>
+      <c r="D3" s="18" t="n"/>
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>and로 한 문장을 만드세요.</t>
         </is>
       </c>
-      <c r="G3" s="21" t="n"/>
-      <c r="H3" s="21" t="n"/>
-      <c r="I3" s="21" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>My mom didn’t let me [stay out] late last night. (stay out)</t>
         </is>
       </c>
-      <c r="C4" s="22" t="n"/>
-      <c r="D4" s="14" t="n"/>
+      <c r="B4" s="21" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>let + 목적어 + 동사원형</t>
+        </is>
+      </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
+          <t>괄호 안의 말을 알맞은 형태로 바꿔 빈칸에 쓰세요.</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="n"/>
+      <c r="G4" s="16" t="n"/>
+      <c r="H4" s="17" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>The long line made the customers [wait] for an hour. (wait)</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>make + 목적어 + 동사원형</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>괄호 안의 말을 알맞은 형태로 바꿔 빈칸에 쓰세요.</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="17" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>The clerk [let] me [exchange] the wallet.</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="n"/>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>그 점원은 내가 지갑을 교환하게 해 주었다.</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
           <t>let + 목적어 + 동사원형</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>괄호 안의 말을 알맞은 형태로 바꿔 빈칸에 쓰세요.</t>
-        </is>
-      </c>
-      <c r="G4" s="17" t="n"/>
-      <c r="H4" s="16" t="n"/>
-      <c r="I4" s="17" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>The long line made the customers [wait] for an hour. (wait)</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>make + 목적어 + 동사원형</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>괄호 안의 말을 알맞은 형태로 바꿔 빈칸에 쓰세요.</t>
-        </is>
-      </c>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="16" t="n"/>
-      <c r="I5" s="17" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>The clerk [let] me [exchange] the wallet.</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>그 점원은 내가 지갑을 교환하게 해 주었다.</t>
-        </is>
-      </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>let + 목적어 + 동사원형</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
           <t>우리말과 같도록 빈칸에 알맞은 말을 쓰세요.</t>
         </is>
       </c>
-      <c r="G6" s="17" t="n"/>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>This scarf is [not] [as|so] expensive [as] that cap.</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>이 스카프는 저 모자만큼 비싸지 않다.</t>
+        </is>
+      </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>이 스카프는 저 모자만큼 비싸지 않다.</t>
+          <t>not as(so) + 원급 + as: ~만큼 …하지 않다</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>not as(so) + 원급 + as: ~만큼 …하지 않다</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
           <t>우리말과 같도록 빈칸에 알맞은 말을 쓰세요.</t>
         </is>
       </c>
-      <c r="G7" s="17" t="n"/>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="n">
-        <v>14</v>
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Tom is 160 cm tall. Jake is 160 cm tall, too.</t>
+        </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Tom is 160 cm tall. Jake is 160 cm tall, too.</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
           <t>Tom is as tall as Jake.|Jake is as tall as Tom.</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>키가 같으면 as tall as</t>
+        </is>
+      </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>키가 같으면 as tall as</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
           <t>두 문장을 as ~ as를 써서 한 문장으로 만드세요.</t>
         </is>
       </c>
-      <c r="G8" s="17" t="n"/>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>My scarf is [as] warm [as] your jacket.</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n"/>
+      <c r="B9" s="21" t="n"/>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>내 목도리는 네 재킷만큼 따뜻하다.</t>
+        </is>
+      </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>내 목도리는 네 재킷만큼 따뜻하다.</t>
+          <t>as + 원급 + as: ~만큼 …한</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>as + 원급 + as: ~만큼 …한</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
           <t>우리말과 같도록 빈칸에 알맞은 말을 쓰세요.</t>
         </is>
       </c>
-      <c r="G9" s="17" t="n"/>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="17" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="I2:I500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
+    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
       <formula1>"사용,검토,보관"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
+    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
       <formula1>5</formula1>
       <formula2>60</formula2>
     </dataValidation>
@@ -3033,55 +2926,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" style="9" min="1" max="1"/>
-    <col width="46" customWidth="1" style="3" min="2" max="2"/>
+    <col width="46" customWidth="1" style="3" min="1" max="1"/>
+    <col width="16" customWidth="1" style="3" min="2" max="2"/>
     <col width="16" customWidth="1" style="3" min="3" max="3"/>
-    <col width="16" customWidth="1" style="3" min="4" max="4"/>
-    <col width="14" customWidth="1" style="3" min="5" max="5"/>
-    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="6" max="8"/>
-    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" style="3" min="4" max="4"/>
+    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="5" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>문장</t>
         </is>
       </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>해설</t>
+        </is>
+      </c>
       <c r="C1" s="11" t="inlineStr">
         <is>
-          <t>해설</t>
+          <t>우리말</t>
         </is>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
-          <t>우리말</t>
-        </is>
-      </c>
-      <c r="E1" s="11" t="inlineStr">
-        <is>
           <t>지시문</t>
         </is>
       </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>시간(초)</t>
+        </is>
+      </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>시간(초)</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="G1" s="12" t="inlineStr">
-        <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -3090,79 +2977,68 @@
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="B2" s="19" t="inlineStr">
-        <is>
           <t>She [go → goes] to school every day.</t>
         </is>
       </c>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>주어가 3인칭 단수면 동사에 -s</t>
         </is>
       </c>
-      <c r="D2" s="19" t="n"/>
-      <c r="E2" s="19" t="n"/>
-      <c r="F2" s="21" t="n"/>
-      <c r="G2" s="21" t="n"/>
-      <c r="H2" s="21" t="n"/>
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="n">
-        <v>6</v>
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>She had her son [to carry → carry] the boxes to the flea market.</t>
+        </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>She had her son [to carry → carry] the boxes to the flea market.</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
           <t>have + 목적어 + 동사원형 (to 없이)</t>
         </is>
       </c>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>어법상 틀린 부분을 찾아 바르게 고치세요.</t>
         </is>
       </c>
-      <c r="F3" s="17" t="n"/>
-      <c r="G3" s="16" t="n"/>
-      <c r="H3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="n">
-        <v>15</v>
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>He runs as [fastly → fast] as his brother.</t>
+        </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>He runs as [fastly → fast] as his brother.</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
           <t>fast는 부사도 fast (fastly는 없는 말)</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>어법상 틀린 부분을 찾아 바르게 고치세요.</t>
         </is>
       </c>
-      <c r="F4" s="17" t="n"/>
-      <c r="G4" s="16" t="n"/>
-      <c r="H4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="17" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
+    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
       <formula1>"사용,검토,보관"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
       <formula1>5</formula1>
       <formula2>60</formula2>
     </dataValidation>
@@ -3178,55 +3054,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" style="9" min="1" max="1"/>
-    <col width="42" customWidth="1" style="3" min="2" max="2"/>
-    <col width="22" customWidth="1" style="3" min="3" max="3"/>
+    <col width="42" customWidth="1" style="3" min="1" max="1"/>
+    <col width="22" customWidth="1" style="3" min="2" max="2"/>
+    <col width="14" customWidth="1" style="3" min="3" max="3"/>
     <col width="14" customWidth="1" style="3" min="4" max="4"/>
-    <col width="14" customWidth="1" style="3" min="5" max="5"/>
-    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="6" max="8"/>
-    <col width="3" customWidth="1" min="9" max="9"/>
+    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="5" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>정답 (조각을 / 로)</t>
         </is>
       </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>우리말</t>
+        </is>
+      </c>
       <c r="C1" s="11" t="inlineStr">
         <is>
-          <t>우리말</t>
+          <t>해설</t>
         </is>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
-          <t>해설</t>
-        </is>
-      </c>
-      <c r="E1" s="11" t="inlineStr">
-        <is>
           <t>지시문</t>
         </is>
       </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>시간(초)</t>
+        </is>
+      </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>시간(초)</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="G1" s="12" t="inlineStr">
-        <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -3235,103 +3105,89 @@
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="B2" s="19" t="inlineStr">
-        <is>
           <t>my mom / makes / me / drink / milk / every day</t>
         </is>
       </c>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>엄마는 내가 매일 우유를 마시게 하신다.</t>
         </is>
       </c>
-      <c r="D2" s="19" t="n"/>
-      <c r="E2" s="19" t="n"/>
-      <c r="F2" s="21" t="n"/>
-      <c r="G2" s="21" t="n"/>
-      <c r="H2" s="21" t="n"/>
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="n">
-        <v>7</v>
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>the clerk / let / me / try on / the scarf</t>
+        </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>the clerk / let / me / try on / the scarf</t>
+          <t>점원은 내가 그 스카프를 착용해 보게 해 주었다.</t>
         </is>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>점원은 내가 그 스카프를 착용해 보게 해 주었다.</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
           <t>let + 목적어 + 동사원형</t>
         </is>
       </c>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="17" t="n"/>
-      <c r="G3" s="16" t="n"/>
-      <c r="H3" s="17" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="n">
-        <v>17</v>
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>I / can / solve / the puzzle / as / easily / as / you</t>
+        </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>I / can / solve / the puzzle / as / easily / as / you</t>
+          <t>나는 너만큼 쉽게 그 퍼즐을 풀 수 있다.</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>나는 너만큼 쉽게 그 퍼즐을 풀 수 있다.</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
           <t>as + 부사 원급 + as</t>
         </is>
       </c>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="17" t="n"/>
-      <c r="G4" s="16" t="n"/>
-      <c r="H4" s="17" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n">
-        <v>20</v>
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>these sneakers / are / not / as / expensive / as / those boots</t>
+        </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>these sneakers / are / not / as / expensive / as / those boots</t>
+          <t>이 운동화는 저 부츠만큼 비싸지 않다.</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>이 운동화는 저 부츠만큼 비싸지 않다.</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
           <t>not as + 원급 + as</t>
         </is>
       </c>
-      <c r="E5" s="14" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="16" t="n"/>
-      <c r="H5" s="17" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="17" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
+    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
       <formula1>"사용,검토,보관"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
       <formula1>5</formula1>
       <formula2>60</formula2>
     </dataValidation>
@@ -3339,483 +3195,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" style="8" min="1" max="1"/>
-    <col width="40" customWidth="1" style="3" min="2" max="2"/>
-    <col width="14" customWidth="1" style="3" min="3" max="3"/>
-    <col width="14" customWidth="1" style="3" min="4" max="4"/>
-    <col width="14" customWidth="1" style="3" min="5" max="5"/>
-    <col width="14" customWidth="1" style="3" min="6" max="6"/>
-    <col width="9" customWidth="1" style="8" min="7" max="7"/>
-    <col width="28" customWidth="1" style="3" min="8" max="8"/>
-    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="9" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>유형</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>문제</t>
-        </is>
-      </c>
-      <c r="C1" s="11" t="inlineStr">
-        <is>
-          <t>보기1</t>
-        </is>
-      </c>
-      <c r="D1" s="11" t="inlineStr">
-        <is>
-          <t>보기2</t>
-        </is>
-      </c>
-      <c r="E1" s="11" t="inlineStr">
-        <is>
-          <t>보기3</t>
-        </is>
-      </c>
-      <c r="F1" s="11" t="inlineStr">
-        <is>
-          <t>보기4</t>
-        </is>
-      </c>
-      <c r="G1" s="10" t="inlineStr">
-        <is>
-          <t>정답</t>
-        </is>
-      </c>
-      <c r="H1" s="11" t="inlineStr">
-        <is>
-          <t>해설</t>
-        </is>
-      </c>
-      <c r="I1" s="12" t="inlineStr">
-        <is>
-          <t>문항ID</t>
-        </is>
-      </c>
-      <c r="J1" s="12" t="inlineStr">
-        <is>
-          <t>피드백1</t>
-        </is>
-      </c>
-      <c r="K1" s="12" t="inlineStr">
-        <is>
-          <t>피드백2</t>
-        </is>
-      </c>
-      <c r="L1" s="12" t="inlineStr">
-        <is>
-          <t>피드백3</t>
-        </is>
-      </c>
-      <c r="M1" s="12" t="inlineStr">
-        <is>
-          <t>피드백4</t>
-        </is>
-      </c>
-      <c r="N1" s="12" t="inlineStr">
-        <is>
-          <t>시간(초)</t>
-        </is>
-      </c>
-      <c r="O1" s="12" t="inlineStr">
-        <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="P1" s="12" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="14" t="n"/>
-      <c r="G2" s="15" t="n"/>
-      <c r="H2" s="14" t="n"/>
-      <c r="I2" s="16" t="n"/>
-      <c r="J2" s="23" t="n"/>
-      <c r="K2" s="23" t="n"/>
-      <c r="L2" s="23" t="n"/>
-      <c r="M2" s="23" t="n"/>
-      <c r="N2" s="17" t="n"/>
-      <c r="O2" s="16" t="n"/>
-      <c r="P2" s="17" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="n"/>
-      <c r="B3" s="14" t="n"/>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="14" t="n"/>
-      <c r="G3" s="15" t="n"/>
-      <c r="H3" s="14" t="n"/>
-      <c r="I3" s="16" t="n"/>
-      <c r="J3" s="23" t="n"/>
-      <c r="K3" s="23" t="n"/>
-      <c r="L3" s="23" t="n"/>
-      <c r="M3" s="23" t="n"/>
-      <c r="N3" s="17" t="n"/>
-      <c r="O3" s="16" t="n"/>
-      <c r="P3" s="17" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="14" t="n"/>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="14" t="n"/>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="14" t="n"/>
-      <c r="I4" s="16" t="n"/>
-      <c r="J4" s="23" t="n"/>
-      <c r="K4" s="23" t="n"/>
-      <c r="L4" s="23" t="n"/>
-      <c r="M4" s="23" t="n"/>
-      <c r="N4" s="17" t="n"/>
-      <c r="O4" s="16" t="n"/>
-      <c r="P4" s="17" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="14" t="n"/>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="14" t="n"/>
-      <c r="F5" s="14" t="n"/>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="14" t="n"/>
-      <c r="I5" s="16" t="n"/>
-      <c r="J5" s="23" t="n"/>
-      <c r="K5" s="23" t="n"/>
-      <c r="L5" s="23" t="n"/>
-      <c r="M5" s="23" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="16" t="n"/>
-      <c r="P5" s="17" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="14" t="n"/>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="14" t="n"/>
-      <c r="E6" s="14" t="n"/>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="14" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="23" t="n"/>
-      <c r="K6" s="23" t="n"/>
-      <c r="L6" s="23" t="n"/>
-      <c r="M6" s="23" t="n"/>
-      <c r="N6" s="17" t="n"/>
-      <c r="O6" s="16" t="n"/>
-      <c r="P6" s="17" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="n"/>
-      <c r="B7" s="14" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="14" t="n"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="14" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="23" t="n"/>
-      <c r="K7" s="23" t="n"/>
-      <c r="L7" s="23" t="n"/>
-      <c r="M7" s="23" t="n"/>
-      <c r="N7" s="17" t="n"/>
-      <c r="O7" s="16" t="n"/>
-      <c r="P7" s="17" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="23" t="n"/>
-      <c r="K8" s="23" t="n"/>
-      <c r="L8" s="23" t="n"/>
-      <c r="M8" s="23" t="n"/>
-      <c r="N8" s="17" t="n"/>
-      <c r="O8" s="16" t="n"/>
-      <c r="P8" s="17" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="n"/>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="23" t="n"/>
-      <c r="K9" s="23" t="n"/>
-      <c r="L9" s="23" t="n"/>
-      <c r="M9" s="23" t="n"/>
-      <c r="N9" s="17" t="n"/>
-      <c r="O9" s="16" t="n"/>
-      <c r="P9" s="17" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="14" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="23" t="n"/>
-      <c r="K10" s="23" t="n"/>
-      <c r="L10" s="23" t="n"/>
-      <c r="M10" s="23" t="n"/>
-      <c r="N10" s="17" t="n"/>
-      <c r="O10" s="16" t="n"/>
-      <c r="P10" s="17" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="14" t="n"/>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="23" t="n"/>
-      <c r="K11" s="23" t="n"/>
-      <c r="L11" s="23" t="n"/>
-      <c r="M11" s="23" t="n"/>
-      <c r="N11" s="17" t="n"/>
-      <c r="O11" s="16" t="n"/>
-      <c r="P11" s="17" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="14" t="n"/>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="23" t="n"/>
-      <c r="K12" s="23" t="n"/>
-      <c r="L12" s="23" t="n"/>
-      <c r="M12" s="23" t="n"/>
-      <c r="N12" s="17" t="n"/>
-      <c r="O12" s="16" t="n"/>
-      <c r="P12" s="17" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="14" t="n"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="14" t="n"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="14" t="n"/>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="23" t="n"/>
-      <c r="K13" s="23" t="n"/>
-      <c r="L13" s="23" t="n"/>
-      <c r="M13" s="23" t="n"/>
-      <c r="N13" s="17" t="n"/>
-      <c r="O13" s="16" t="n"/>
-      <c r="P13" s="17" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="14" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="23" t="n"/>
-      <c r="K14" s="23" t="n"/>
-      <c r="L14" s="23" t="n"/>
-      <c r="M14" s="23" t="n"/>
-      <c r="N14" s="17" t="n"/>
-      <c r="O14" s="16" t="n"/>
-      <c r="P14" s="17" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="14" t="n"/>
-      <c r="I15" s="16" t="n"/>
-      <c r="J15" s="23" t="n"/>
-      <c r="K15" s="23" t="n"/>
-      <c r="L15" s="23" t="n"/>
-      <c r="M15" s="23" t="n"/>
-      <c r="N15" s="17" t="n"/>
-      <c r="O15" s="16" t="n"/>
-      <c r="P15" s="17" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="14" t="n"/>
-      <c r="I16" s="16" t="n"/>
-      <c r="J16" s="23" t="n"/>
-      <c r="K16" s="23" t="n"/>
-      <c r="L16" s="23" t="n"/>
-      <c r="M16" s="23" t="n"/>
-      <c r="N16" s="17" t="n"/>
-      <c r="O16" s="16" t="n"/>
-      <c r="P16" s="17" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-      <c r="H17" s="14" t="n"/>
-      <c r="I17" s="16" t="n"/>
-      <c r="J17" s="23" t="n"/>
-      <c r="K17" s="23" t="n"/>
-      <c r="L17" s="23" t="n"/>
-      <c r="M17" s="23" t="n"/>
-      <c r="N17" s="17" t="n"/>
-      <c r="O17" s="16" t="n"/>
-      <c r="P17" s="17" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="14" t="n"/>
-      <c r="I18" s="16" t="n"/>
-      <c r="J18" s="23" t="n"/>
-      <c r="K18" s="23" t="n"/>
-      <c r="L18" s="23" t="n"/>
-      <c r="M18" s="23" t="n"/>
-      <c r="N18" s="17" t="n"/>
-      <c r="O18" s="16" t="n"/>
-      <c r="P18" s="17" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="14" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="14" t="n"/>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="14" t="n"/>
-      <c r="I19" s="16" t="n"/>
-      <c r="J19" s="23" t="n"/>
-      <c r="K19" s="23" t="n"/>
-      <c r="L19" s="23" t="n"/>
-      <c r="M19" s="23" t="n"/>
-      <c r="N19" s="17" t="n"/>
-      <c r="O19" s="16" t="n"/>
-      <c r="P19" s="17" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="n"/>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="14" t="n"/>
-      <c r="I20" s="16" t="n"/>
-      <c r="J20" s="23" t="n"/>
-      <c r="K20" s="23" t="n"/>
-      <c r="L20" s="23" t="n"/>
-      <c r="M20" s="23" t="n"/>
-      <c r="N20" s="17" t="n"/>
-      <c r="O20" s="16" t="n"/>
-      <c r="P20" s="17" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="n"/>
-      <c r="B21" s="14" t="n"/>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="14" t="n"/>
-      <c r="E21" s="14" t="n"/>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
-      <c r="H21" s="14" t="n"/>
-      <c r="I21" s="16" t="n"/>
-      <c r="J21" s="23" t="n"/>
-      <c r="K21" s="23" t="n"/>
-      <c r="L21" s="23" t="n"/>
-      <c r="M21" s="23" t="n"/>
-      <c r="N21" s="17" t="n"/>
-      <c r="O21" s="16" t="n"/>
-      <c r="P21" s="17" t="n"/>
-    </row>
-  </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="P2:P500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
-      <formula1>"사용,검토,보관"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
-      <formula1>5</formula1>
-      <formula2>60</formula2>
-    </dataValidation>
-    <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="유형" error="객관식, OX, 단답형 중에서 고르세요." type="list">
-      <formula1>"객관식,OX,단답형"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/templates/M2_L7.xlsx
+++ b/templates/M2_L7.xlsx
@@ -289,7 +289,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>13</col>
+      <col>12</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -319,7 +319,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
@@ -349,7 +349,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>(try / to try)처럼 괄호에 보기를 넣거나, 보기1~4에 문장을 써요(정답은 번호). 정답이 O·X(T·F)면 OX 문제 → 운동장에서 고르기</t>
+          <t>(try / to try)처럼 괄호에 보기를 넣거나, 보기1~4에 문장을 써요(정답은 번호, 문장 칸엔 질문). 정답이 O·X(T·F)면 OX 문제 → 운동장에서 고르기</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>정답 문장을 조각마다 / 로 나눠요. 첫 조각도 소문자로: the clerk / let / me → 폰에서 조각을 순서대로 누르기</t>
+          <t>정답 문장을 조각마다 / 로 나누고, 우리말 칸에 뜻을 써요. 첫 조각도 소문자로: the clerk / let / me → 폰에서 조각을 순서대로 누르기</t>
         </is>
       </c>
     </row>
@@ -793,90 +793,99 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>노란 머리글은 늘 쓰는 칸, 연회색 머리글은 필요할 때 쓰는 칸(보기·정답·해설·지시문·우리말)이에요. 거의 안 쓰는 칸(시간·세트·상태 등)은 오른쪽에 접어 두었어요(표 위 + 를 누르면 보여요).</t>
+          <t>먼저 보여 줄 정보나 우리말 뜻은 문장 칸에서 줄을 바꿔(Alt+Enter, 맥은 ⌥+Enter) 위에 쓰고, 문제 문장은 맨 아래 줄에 써요.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>파란 줄은 예시라서 문제로 나오지 않아요. 예시 줄을 복사해 쓸 때는 내용을 고쳐 쓰면 문제가 돼요.</t>
+          <t>노란 머리글은 늘 쓰는 칸, 연회색 머리글은 필요할 때 쓰는 칸(보기·정답·해설·지시문)이에요. 거의 안 쓰는 칸(시간·세트·상태 등)은 오른쪽에 접어 두었어요(표 위 + 를 누르면 보여요).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>답을 여러 개 인정하려면 | 로 나눠요: [as|so]  ·  Tom is as tall as Jake.|Jake is as tall as Tom.</t>
+          <t>파란 줄은 예시라서 문제로 나오지 않아요. 예시 줄을 복사해 쓸 때는 내용을 고쳐 쓰면 문제가 돼요.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>문제는 단어 → 문법 고르기 → 쓰기 → 고치기 → 배열 순서로 나오고, 같은 탭 안에서는 앱이 순서를 섞어요.</t>
+          <t>답을 여러 개 인정하려면 | 로 나눠요: [as|so]  ·  Tom is as tall as Jake.|Jake is as tall as Tom.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>문제는 단어 → 문법 고르기 → 쓰기 → 고치기 → 배열 순서로 나오고, 같은 탭 안에서는 앱이 순서를 섞어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>단어장과 문법 탭의 표 오른쪽에 '이렇게 나와요' 화면 예시(프로젝터 · 학생 폰)가 있어요.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>AI로 내 파일 만들기</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>1. AI(챗GPT·Gemini·Claude 등)에 이 파일과 내 자료(본문·단어·문법 문제)를 함께 올려요.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2. 아래 칸의 부탁 글을 복사해 붙여 넣어요.</t>
+          <t>1. AI(챗GPT·Gemini·Claude 등)에 이 파일과 내 자료(본문·단어·문법 문제)를 함께 올려요.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>2. 아래 칸의 부탁 글을 복사해 붙여 넣어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
           <t>3. 받은 파일을 [엑셀 올리기]로 올리고, 미리보기에서 문제와 정답을 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="116" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="24" ht="132" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>첨부한 M2_L7.xlsx와 똑같은 형식으로, 첨부한 내 자료의 퀴즈 파일을 만들어 줘.
 - 탭 이름, 머리글, 탭 순서, 열 순서는 그대로 두고, 열을 더하거나 셀을 합치지 마.
 - 각 탭 맨 위의 파란 예시 줄은 그대로 두고, 그 아래 7과 내용만 지우고 내 자료로 채워.
 - 안내 탭의 표시를 그대로 써: 고르기 (A / B), 쓰기 [답], 고치기 [틀린 말 → 고친 말](표시는 4곳까지), 배열 조각 / 조각(첫 조각도 소문자).
+- 먼저 보여 줄 정보나 우리말 뜻은 문장 칸 안에서 줄을 바꿔 문제 문장 위에 써. 우리말 칸은 배열 탭에만 있어.
 - 한 줄에 한 문제. 여러 답은 | 로 나누고, 정답은 문장 속 표시와 꼭 맞게 써. 모르는 칸은 비워 둬.
 - 파일 이름은 M2_L8.xlsx처럼 학년_단원으로 해 줘.</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A20:B20"/>
+  <mergeCells count="12">
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A22:B22"/>
   </mergeCells>
@@ -890,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="8" min="1" max="1"/>
@@ -1378,823 +1387,6 @@
       <c r="I16" s="16" t="n"/>
       <c r="J16" s="17" t="n"/>
       <c r="K16" s="16" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>give away</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>무료로 주다</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="n"/>
-      <c r="I17" s="16" t="n"/>
-      <c r="J17" s="17" t="n"/>
-      <c r="K17" s="16" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>secondhand</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>중고의</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>형</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="n"/>
-      <c r="I18" s="16" t="n"/>
-      <c r="J18" s="17" t="n"/>
-      <c r="K18" s="16" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>rental</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>임대, 대여</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>명</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="n"/>
-      <c r="I19" s="16" t="n"/>
-      <c r="J19" s="17" t="n"/>
-      <c r="K19" s="16" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>rent</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>빌리다, 임차하다</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>동</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="n"/>
-      <c r="I20" s="16" t="n"/>
-      <c r="J20" s="17" t="n"/>
-      <c r="K20" s="16" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>lock</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>자물쇠</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="14" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>명</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="n"/>
-      <c r="I21" s="16" t="n"/>
-      <c r="J21" s="17" t="n"/>
-      <c r="K21" s="16" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>spend</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>(돈을) 쓰다</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="14" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>동</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="n"/>
-      <c r="I22" s="16" t="n"/>
-      <c r="J22" s="17" t="n"/>
-      <c r="K22" s="16" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>scan</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>스캔하다, 훑다</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="14" t="n"/>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
-          <t>동</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="n"/>
-      <c r="I23" s="16" t="n"/>
-      <c r="J23" s="17" t="n"/>
-      <c r="K23" s="16" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>allow</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>허락하다, 가능하게 하다</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>동</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="n"/>
-      <c r="I24" s="16" t="n"/>
-      <c r="J24" s="17" t="n"/>
-      <c r="K24" s="16" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>easily</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>쉽게</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>부</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="n"/>
-      <c r="I25" s="16" t="n"/>
-      <c r="J25" s="17" t="n"/>
-      <c r="K25" s="16" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>무료의</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="14" t="n"/>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>형</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="n"/>
-      <c r="I26" s="16" t="n"/>
-      <c r="J26" s="17" t="n"/>
-      <c r="K26" s="16" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>instead of</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>~ 대신에</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="14" t="n"/>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="n"/>
-      <c r="I27" s="16" t="n"/>
-      <c r="J27" s="17" t="n"/>
-      <c r="K27" s="16" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>in good condition</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>상태가 좋은</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="n"/>
-      <c r="D28" s="14" t="n"/>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="n"/>
-      <c r="I28" s="16" t="n"/>
-      <c r="J28" s="17" t="n"/>
-      <c r="K28" s="16" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>head for</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>~로 향하다</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="14" t="n"/>
-      <c r="E29" s="15" t="n"/>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="n"/>
-      <c r="I29" s="16" t="n"/>
-      <c r="J29" s="17" t="n"/>
-      <c r="K29" s="16" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>명</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="n"/>
-      <c r="I30" s="16" t="n"/>
-      <c r="J30" s="17" t="n"/>
-      <c r="K30" s="16" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>wallet</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>지갑</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="14" t="n"/>
-      <c r="E31" s="15" t="inlineStr">
-        <is>
-          <t>명</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="n"/>
-      <c r="I31" s="16" t="n"/>
-      <c r="J31" s="17" t="n"/>
-      <c r="K31" s="16" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>현금</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>명</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H32" s="17" t="n"/>
-      <c r="I32" s="16" t="n"/>
-      <c r="J32" s="17" t="n"/>
-      <c r="K32" s="16" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>scratch</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>긁힌 자국</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="14" t="n"/>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t>명</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="n"/>
-      <c r="I33" s="16" t="n"/>
-      <c r="J33" s="17" t="n"/>
-      <c r="K33" s="16" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>stay out</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>(밤에) 집 밖에 있다</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="14" t="n"/>
-      <c r="E34" s="15" t="n"/>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H34" s="17" t="n"/>
-      <c r="I34" s="16" t="n"/>
-      <c r="J34" s="17" t="n"/>
-      <c r="K34" s="16" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>water</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>(식물에) 물을 주다</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="14" t="n"/>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
-          <t>동</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="n"/>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H35" s="17" t="n"/>
-      <c r="I35" s="16" t="n"/>
-      <c r="J35" s="17" t="n"/>
-      <c r="K35" s="16" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>lake</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>호수</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>명</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="n"/>
-      <c r="G36" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H36" s="17" t="n"/>
-      <c r="I36" s="16" t="n"/>
-      <c r="J36" s="17" t="n"/>
-      <c r="K36" s="16" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
-        <is>
-          <t>forget</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>잊다</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n"/>
-      <c r="D37" s="14" t="n"/>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>동</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="n"/>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H37" s="17" t="n"/>
-      <c r="I37" s="16" t="n"/>
-      <c r="J37" s="17" t="n"/>
-      <c r="K37" s="16" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>scarf</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>목도리, 스카프</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="14" t="n"/>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>명</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="n"/>
-      <c r="G38" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H38" s="17" t="n"/>
-      <c r="I38" s="16" t="n"/>
-      <c r="J38" s="17" t="n"/>
-      <c r="K38" s="16" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>sneaker</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>운동화</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="n"/>
-      <c r="D39" s="14" t="n"/>
-      <c r="E39" s="15" t="inlineStr">
-        <is>
-          <t>명</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="n"/>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H39" s="17" t="n"/>
-      <c r="I39" s="16" t="n"/>
-      <c r="J39" s="17" t="n"/>
-      <c r="K39" s="16" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>boot</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>부츠, 장화</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n"/>
-      <c r="D40" s="14" t="n"/>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>명</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="n"/>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H40" s="17" t="n"/>
-      <c r="I40" s="16" t="n"/>
-      <c r="J40" s="17" t="n"/>
-      <c r="K40" s="16" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>go well with</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>~와 잘 어울리다</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n"/>
-      <c r="D41" s="14" t="n"/>
-      <c r="E41" s="15" t="n"/>
-      <c r="F41" s="14" t="n"/>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H41" s="17" t="n"/>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="17" t="n"/>
-      <c r="K41" s="16" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="13" t="inlineStr">
-        <is>
-          <t>gray</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>회색의</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n"/>
-      <c r="D42" s="14" t="n"/>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
-          <t>형</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="n"/>
-      <c r="G42" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H42" s="17" t="n"/>
-      <c r="I42" s="16" t="n"/>
-      <c r="J42" s="17" t="n"/>
-      <c r="K42" s="16" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>daughter</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>딸</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n"/>
-      <c r="D43" s="14" t="n"/>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>명</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="n"/>
-      <c r="G43" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H43" s="17" t="n"/>
-      <c r="I43" s="16" t="n"/>
-      <c r="J43" s="17" t="n"/>
-      <c r="K43" s="16" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>expensive</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>비싼</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="n"/>
-      <c r="D44" s="14" t="n"/>
-      <c r="E44" s="15" t="inlineStr">
-        <is>
-          <t>형</t>
-        </is>
-      </c>
-      <c r="F44" s="14" t="n"/>
-      <c r="G44" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H44" s="17" t="n"/>
-      <c r="I44" s="16" t="n"/>
-      <c r="J44" s="17" t="n"/>
-      <c r="K44" s="16" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="13" t="inlineStr">
-        <is>
-          <t>wise</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>현명한, 지혜로운</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="n"/>
-      <c r="D45" s="14" t="n"/>
-      <c r="E45" s="15" t="inlineStr">
-        <is>
-          <t>형</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="n"/>
-      <c r="G45" s="16" t="inlineStr">
-        <is>
-          <t>Lesson 7</t>
-        </is>
-      </c>
-      <c r="H45" s="17" t="n"/>
-      <c r="I45" s="16" t="n"/>
-      <c r="J45" s="17" t="n"/>
-      <c r="K45" s="16" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -2220,10 +1412,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" style="3" min="1" max="1"/>
+    <col width="44" customWidth="1" style="3" min="1" max="1"/>
     <col width="9" customWidth="1" style="8" min="2" max="2"/>
     <col width="11" customWidth="1" style="3" min="3" max="3"/>
     <col width="11" customWidth="1" style="3" min="4" max="4"/>
@@ -2231,9 +1423,8 @@
     <col width="11" customWidth="1" style="3" min="6" max="6"/>
     <col width="13" customWidth="1" style="3" min="7" max="7"/>
     <col width="12" customWidth="1" style="3" min="8" max="8"/>
-    <col width="12" customWidth="1" style="3" min="9" max="9"/>
-    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="10" max="12"/>
-    <col width="3" customWidth="1" min="13" max="13"/>
+    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="9" max="11"/>
+    <col width="3" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2277,22 +1468,17 @@
           <t>지시문</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
-        <is>
-          <t>우리말</t>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>시간(초)</t>
         </is>
       </c>
       <c r="J1" s="12" t="inlineStr">
         <is>
-          <t>시간(초)</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="K1" s="12" t="inlineStr">
-        <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -2319,13 +1505,16 @@
         </is>
       </c>
       <c r="H2" s="18" t="n"/>
-      <c r="I2" s="18" t="n"/>
+      <c r="I2" s="20" t="n"/>
       <c r="J2" s="20" t="n"/>
       <c r="K2" s="20" t="n"/>
-      <c r="L2" s="20" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n"/>
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>바른 문장을 고르세요.</t>
+        </is>
+      </c>
       <c r="B3" s="19" t="inlineStr">
         <is>
           <t>2</t>
@@ -2348,20 +1537,16 @@
           <t>주어가 3인칭 단수면 동사에 -s</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
-        <is>
-          <t>바른 문장을 고르세요.</t>
-        </is>
-      </c>
-      <c r="I3" s="18" t="n"/>
+      <c r="H3" s="18" t="n"/>
+      <c r="I3" s="20" t="n"/>
       <c r="J3" s="20" t="n"/>
       <c r="K3" s="20" t="n"/>
-      <c r="L3" s="20" t="n"/>
-    </row>
-    <row r="4">
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>Bag A is as heavy as Bag B.</t>
+          <t>가방 A 3kg, 가방 B 3kg
+Bag A is as heavy as Bag B.</t>
         </is>
       </c>
       <c r="B4" s="19" t="inlineStr">
@@ -2375,14 +1560,9 @@
       <c r="F4" s="18" t="n"/>
       <c r="G4" s="18" t="n"/>
       <c r="H4" s="18" t="n"/>
-      <c r="I4" s="18" t="inlineStr">
-        <is>
-          <t>가방 A 3kg, 가방 B 3kg</t>
-        </is>
-      </c>
+      <c r="I4" s="20" t="n"/>
       <c r="J4" s="20" t="n"/>
       <c r="K4" s="20" t="n"/>
-      <c r="L4" s="20" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -2405,10 +1585,9 @@
         </is>
       </c>
       <c r="H5" s="14" t="n"/>
-      <c r="I5" s="14" t="n"/>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="16" t="n"/>
-      <c r="L5" s="17" t="n"/>
+      <c r="I5" s="17" t="n"/>
+      <c r="J5" s="16" t="n"/>
+      <c r="K5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -2431,10 +1610,9 @@
         </is>
       </c>
       <c r="H6" s="14" t="n"/>
-      <c r="I6" s="14" t="n"/>
-      <c r="J6" s="17" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="17" t="n"/>
+      <c r="I6" s="17" t="n"/>
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
@@ -2457,13 +1635,16 @@
         </is>
       </c>
       <c r="H7" s="14" t="n"/>
-      <c r="I7" s="14" t="n"/>
-      <c r="J7" s="17" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n"/>
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>어법상 바른 문장을 고르세요.</t>
+        </is>
+      </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
           <t>2</t>
@@ -2486,15 +1667,10 @@
           <t>make + 목적어 + 동사원형 (to 없이)</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>어법상 바른 문장을 고르세요.</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="n"/>
-      <c r="J8" s="17" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="17" t="n"/>
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="17" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
@@ -2517,10 +1693,9 @@
         </is>
       </c>
       <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
-      <c r="J9" s="17" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
@@ -2543,13 +1718,16 @@
         </is>
       </c>
       <c r="H10" s="14" t="n"/>
-      <c r="I10" s="14" t="n"/>
-      <c r="J10" s="17" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="17" t="n"/>
+      <c r="I10" s="17" t="n"/>
+      <c r="J10" s="16" t="n"/>
+      <c r="K10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n"/>
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>어법상 바른 문장을 고르세요.</t>
+        </is>
+      </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
           <t>1</t>
@@ -2572,20 +1750,16 @@
           <t>as ~ as 사이에는 원급</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>어법상 바른 문장을 고르세요.</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="n"/>
-      <c r="J11" s="17" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="17" t="n"/>
-    </row>
-    <row r="12">
+      <c r="H11" s="14" t="n"/>
+      <c r="I11" s="17" t="n"/>
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="17" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Mirror A is as expensive as Mirror B.</t>
+          <t>거울 A: $20 / 거울 B: $30
+Mirror A is as expensive as Mirror B.</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -2607,14 +1781,9 @@
           <t>다음 정보를 보고 문장이 맞으면 T, 틀리면 F를 고르세요.</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>거울 A: $20 / 거울 B: $30</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="17" t="n"/>
+      <c r="I12" s="17" t="n"/>
+      <c r="J12" s="16" t="n"/>
+      <c r="K12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -2637,17 +1806,16 @@
         </is>
       </c>
       <c r="H13" s="14" t="n"/>
-      <c r="I13" s="14" t="n"/>
-      <c r="J13" s="17" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="17" t="n"/>
+      <c r="I13" s="17" t="n"/>
+      <c r="J13" s="16" t="n"/>
+      <c r="K13" s="17" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
+    <dataValidation sqref="K2:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
       <formula1>"사용,검토,보관"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
+    <dataValidation sqref="I2:I500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
       <formula1>5</formula1>
       <formula2>60</formula2>
     </dataValidation>
@@ -2663,16 +1831,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" style="3" min="1" max="1"/>
+    <col width="46" customWidth="1" style="3" min="1" max="1"/>
     <col width="18" customWidth="1" style="3" min="2" max="2"/>
-    <col width="16" customWidth="1" style="3" min="3" max="3"/>
+    <col width="14" customWidth="1" style="3" min="3" max="3"/>
     <col width="14" customWidth="1" style="3" min="4" max="4"/>
-    <col width="14" customWidth="1" style="3" min="5" max="5"/>
-    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="6" max="8"/>
-    <col width="3" customWidth="1" min="9" max="9"/>
+    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="5" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2688,52 +1855,43 @@
       </c>
       <c r="C1" s="11" t="inlineStr">
         <is>
-          <t>우리말</t>
+          <t>해설</t>
         </is>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
-          <t>해설</t>
-        </is>
-      </c>
-      <c r="E1" s="11" t="inlineStr">
-        <is>
           <t>지시문</t>
         </is>
       </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>시간(초)</t>
+        </is>
+      </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>시간(초)</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="G1" s="12" t="inlineStr">
         <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="H1" s="12" t="inlineStr">
-        <is>
           <t>상태</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>He [doesn't] like milk.</t>
+          <t>그는 우유를 좋아하지 않는다.
+He [doesn't] like milk.</t>
         </is>
       </c>
       <c r="B2" s="18" t="n"/>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>그는 우유를 좋아하지 않는다.</t>
-        </is>
-      </c>
+      <c r="C2" s="18" t="n"/>
       <c r="D2" s="18" t="n"/>
-      <c r="E2" s="18" t="n"/>
+      <c r="E2" s="20" t="n"/>
       <c r="F2" s="20" t="n"/>
       <c r="G2" s="20" t="n"/>
-      <c r="H2" s="20" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
@@ -2747,15 +1905,14 @@
         </is>
       </c>
       <c r="C3" s="18" t="n"/>
-      <c r="D3" s="18" t="n"/>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>and로 한 문장을 만드세요.</t>
         </is>
       </c>
+      <c r="E3" s="20" t="n"/>
       <c r="F3" s="20" t="n"/>
       <c r="G3" s="20" t="n"/>
-      <c r="H3" s="20" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
@@ -2764,20 +1921,19 @@
         </is>
       </c>
       <c r="B4" s="21" t="n"/>
-      <c r="C4" s="14" t="n"/>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>let + 목적어 + 동사원형</t>
+        </is>
+      </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>let + 목적어 + 동사원형</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
           <t>괄호 안의 말을 알맞은 형태로 바꿔 빈칸에 쓰세요.</t>
         </is>
       </c>
-      <c r="F4" s="17" t="n"/>
-      <c r="G4" s="16" t="n"/>
-      <c r="H4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="17" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -2786,72 +1942,63 @@
         </is>
       </c>
       <c r="B5" s="21" t="n"/>
-      <c r="C5" s="14" t="n"/>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>make + 목적어 + 동사원형</t>
+        </is>
+      </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>make + 목적어 + 동사원형</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
           <t>괄호 안의 말을 알맞은 형태로 바꿔 빈칸에 쓰세요.</t>
         </is>
       </c>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="16" t="n"/>
-      <c r="H5" s="17" t="n"/>
-    </row>
-    <row r="6">
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="17" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>The clerk [let] me [exchange] the wallet.</t>
+          <t>그 점원은 내가 지갑을 교환하게 해 주었다.
+The clerk [let] me [exchange] the wallet.</t>
         </is>
       </c>
       <c r="B6" s="21" t="n"/>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>그 점원은 내가 지갑을 교환하게 해 주었다.</t>
+          <t>let + 목적어 + 동사원형</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>let + 목적어 + 동사원형</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
           <t>우리말과 같도록 빈칸에 알맞은 말을 쓰세요.</t>
         </is>
       </c>
-      <c r="F6" s="17" t="n"/>
-      <c r="G6" s="16" t="n"/>
-      <c r="H6" s="17" t="n"/>
-    </row>
-    <row r="7">
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>This scarf is [not] [as|so] expensive [as] that cap.</t>
+          <t>이 스카프는 저 모자만큼 비싸지 않다.
+This scarf is [not] [as|so] expensive [as] that cap.</t>
         </is>
       </c>
       <c r="B7" s="21" t="n"/>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>이 스카프는 저 모자만큼 비싸지 않다.</t>
+          <t>not as(so) + 원급 + as: ~만큼 …하지 않다</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>not as(so) + 원급 + as: ~만큼 …하지 않다</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
           <t>우리말과 같도록 빈칸에 알맞은 말을 쓰세요.</t>
         </is>
       </c>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="16" t="n"/>
-      <c r="H7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
@@ -2864,53 +2011,48 @@
           <t>Tom is as tall as Jake.|Jake is as tall as Tom.</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n"/>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>키가 같으면 as tall as</t>
+        </is>
+      </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>키가 같으면 as tall as</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
           <t>두 문장을 as ~ as를 써서 한 문장으로 만드세요.</t>
         </is>
       </c>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="17" t="n"/>
-    </row>
-    <row r="9">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="17" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>My scarf is [as] warm [as] your jacket.</t>
+          <t>내 목도리는 네 재킷만큼 따뜻하다.
+My scarf is [as] warm [as] your jacket.</t>
         </is>
       </c>
       <c r="B9" s="21" t="n"/>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>내 목도리는 네 재킷만큼 따뜻하다.</t>
+          <t>as + 원급 + as: ~만큼 …한</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>as + 원급 + as: ~만큼 …한</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
           <t>우리말과 같도록 빈칸에 알맞은 말을 쓰세요.</t>
         </is>
       </c>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="17" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
+    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
       <formula1>"사용,검토,보관"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
       <formula1>5</formula1>
       <formula2>60</formula2>
     </dataValidation>
@@ -2926,15 +2068,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="3" min="1" max="1"/>
     <col width="16" customWidth="1" style="3" min="2" max="2"/>
-    <col width="16" customWidth="1" style="3" min="3" max="3"/>
-    <col width="14" customWidth="1" style="3" min="4" max="4"/>
-    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="5" max="7"/>
-    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" style="3" min="3" max="3"/>
+    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="4" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2950,25 +2091,20 @@
       </c>
       <c r="C1" s="11" t="inlineStr">
         <is>
-          <t>우리말</t>
-        </is>
-      </c>
-      <c r="D1" s="11" t="inlineStr">
-        <is>
           <t>지시문</t>
         </is>
       </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>시간(초)</t>
+        </is>
+      </c>
       <c r="E1" s="12" t="inlineStr">
         <is>
-          <t>시간(초)</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F1" s="12" t="inlineStr">
-        <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -2986,10 +2122,9 @@
         </is>
       </c>
       <c r="C2" s="18" t="n"/>
-      <c r="D2" s="18" t="n"/>
+      <c r="D2" s="20" t="n"/>
       <c r="E2" s="20" t="n"/>
       <c r="F2" s="20" t="n"/>
-      <c r="G2" s="20" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
@@ -3002,15 +2137,14 @@
           <t>have + 목적어 + 동사원형 (to 없이)</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>어법상 틀린 부분을 찾아 바르게 고치세요.</t>
         </is>
       </c>
-      <c r="E3" s="17" t="n"/>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
@@ -3023,22 +2157,21 @@
           <t>fast는 부사도 fast (fastly는 없는 말)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>어법상 틀린 부분을 찾아 바르게 고치세요.</t>
         </is>
       </c>
-      <c r="E4" s="17" t="n"/>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
+    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
       <formula1>"사용,검토,보관"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
+    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
       <formula1>5</formula1>
       <formula2>60</formula2>
     </dataValidation>
@@ -3071,7 +2204,7 @@
           <t>정답 (조각을 / 로)</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>우리말</t>
         </is>

--- a/templates/M2_L7.xlsx
+++ b/templates/M2_L7.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -169,9 +169,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -349,7 +346,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -719,102 +716,102 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>탭마다 쓰는 법</t>
+          <t>쓰는 법: 한 줄에 한 문제, 문장과 정답 한 쌍</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>단어장</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>단어와 뜻만 쓰면 문제와 오답 보기는 앱이 만들어요. 예문은 빈칸 자리를 [ ]로: Can I [borrow] your pen?</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>시험지의 문제는 문장 칸에, 답지의 답은 정답 칸에 그대로 써요. 먼저 보여 줄 우리말이나 정보는 문장 칸에서 줄을 바꿔 위에 써요(셀을 두 번 누르고 Alt+Enter, 맥 엑셀은 Control+Option+Return).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>문법 고르기</t>
+          <t>단어장</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>(try / to try)처럼 괄호에 보기를 넣거나, 보기1~4에 문장을 써요(정답은 번호, 문장 칸엔 질문). 정답이 O·X(T·F)면 OX 문제 → 운동장에서 고르기</t>
+          <t>단어와 뜻. 예문은 단어가 그대로 들어간 문장을 쓰면 앱이 단어 자리를 빈칸으로 만들어요(단어가 두 번 나오면 그 자리를 ___로). 문제와 오답 보기는 앱이 만들어요.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>문법 쓰기</t>
+          <t>문법 고르기</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>답 자리를 [ ]로 감싸요: The clerk [let] me go. [ ]가 없으면 정답 칸에 답을 써요 → 폰에 쓰기</t>
+          <t>The clerk let me (try / to try) on the sneakers.  → 정답 try   ·   보기1~4에 문장을 쓰면 정답은 번호(문장 칸엔 질문)   ·   정답이 O·X(T·F)면 OX 문제</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>문법 고치기</t>
+          <t>문법 쓰기</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>틀린 곳을 [틀린 말 → 고친 말]로(-&gt; 도 돼요): He runs as [fastly → fast] as me. 빼야 하는 말은 [to →]. 헷갈리게 할 곳은 [ ]로 3곳까지 → 틀린 곳 찾기, 이어서 고쳐 쓰기</t>
+          <t>The clerk ___ me ___ the wallet.  → 정답 let, exchange (빈칸 순서대로 쉼표)   ·   빈칸이 없으면 정답에 완성 문장</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t>문법 고치기</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>He runs as fastly as his brother.  → 정답 fastly → fast   ·   빼야 하는 말은 to → 삭제   ·   같은 말이 두 번 있으면 옆 낱말과 함께: to carry → carry</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
           <t>문법 배열</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>정답 문장을 조각마다 / 로 나누고, 우리말 칸에 뜻을 써요. 첫 조각도 소문자로: the clerk / let / me → 폰에서 조각을 순서대로 누르기</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>우리말 (줄 바꿈) (let / me / the clerk / try on / the scarf)  → 정답 The clerk let me try on the scarf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>알아 두기</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>먼저 보여 줄 정보나 우리말 뜻은 문장 칸에서 줄을 바꿔(Alt+Enter, 맥은 ⌥+Enter) 위에 쓰고, 문제 문장은 맨 아래 줄에 써요.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>노란 머리글은 늘 쓰는 칸, 연회색 머리글은 필요할 때 쓰는 칸(보기·정답·해설·지시문)이에요. 거의 안 쓰는 칸(시간·세트·상태 등)은 오른쪽에 접어 두었어요(표 위 + 를 누르면 보여요).</t>
+          <t>/ 는 보기와 조각을 나누고, 쉼표는 빈칸 답의 순서예요. 다른 답도 인정하려면 | (Shift+₩)로 나눠요: as|so  ·  Tom is as tall as Jake.|Jake is as tall as Tom.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>파란 줄은 예시라서 문제로 나오지 않아요. 예시 줄을 복사해 쓸 때는 내용을 고쳐 쓰면 문제가 돼요.</t>
+          <t>노란 머리글(문장·정답)은 늘 쓰는 칸, 연회색 머리글은 필요할 때 쓰는 칸(보기·해설·지시문)이에요. 지시문을 비우면 앱이 알맞은 지시문을 넣어요. 거의 안 쓰는 칸(시간·세트·상태 등)은 오른쪽에 접어 두었어요(표 위 + 를 누르면 보여요).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>답을 여러 개 인정하려면 | 로 나눠요: [as|so]  ·  Tom is as tall as Jake.|Jake is as tall as Tom.</t>
+          <t>파란 줄은 예시라서 문제로 나오지 않아요. 예시 줄을 복사해 쓸 때는 내용을 고쳐 쓰면 문제가 돼요.</t>
         </is>
       </c>
     </row>
@@ -860,15 +857,15 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="132" customHeight="1">
+    <row r="24" ht="150" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t>첨부한 M2_L7.xlsx와 똑같은 형식으로, 첨부한 내 자료의 퀴즈 파일을 만들어 줘.
 - 탭 이름, 머리글, 탭 순서, 열 순서는 그대로 두고, 열을 더하거나 셀을 합치지 마.
 - 각 탭 맨 위의 파란 예시 줄은 그대로 두고, 그 아래 7과 내용만 지우고 내 자료로 채워.
-- 안내 탭의 표시를 그대로 써: 고르기 (A / B), 쓰기 [답], 고치기 [틀린 말 → 고친 말](표시는 4곳까지), 배열 조각 / 조각(첫 조각도 소문자).
-- 먼저 보여 줄 정보나 우리말 뜻은 문장 칸 안에서 줄을 바꿔 문제 문장 위에 써. 우리말 칸은 배열 탭에만 있어.
-- 한 줄에 한 문제. 여러 답은 | 로 나누고, 정답은 문장 속 표시와 꼭 맞게 써. 모르는 칸은 비워 둬.
+- 한 줄에 한 문제: 문제는 문장 칸, 답은 정답 칸, 지시문은 지시문 칸에 써.
+- 고르기는 문장에 (A / B), 정답에 고른 말. 쓰기는 빈칸을 ___로, 정답에 답(빈칸이 여럿이면 순서대로 쉼표). 고치기는 문장을 틀린 그대로, 정답에 "틀린 말 → 고친 말"(한 줄에 하나: 틀린 곳이 둘이면 두 줄로 나누고 다른 쪽은 고친 채로). 배열은 문장에 우리말, 줄을 바꿔 (조각 / 조각 / …), 정답에 완성 문장.
+- 먼저 보여 줄 우리말이나 정보는 문장 칸 안에서 줄을 바꿔 위에 써. 다른 답도 인정하면 | 로 나눠. 모르는 칸은 비워 둬.
 - 파일 이름은 M2_L8.xlsx처럼 학년_단원으로 해 줘.</t>
         </is>
       </c>
@@ -881,12 +878,12 @@
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1416,7 +1413,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" style="3" min="1" max="1"/>
-    <col width="9" customWidth="1" style="8" min="2" max="2"/>
+    <col width="14" customWidth="1" style="3" min="2" max="2"/>
     <col width="11" customWidth="1" style="3" min="3" max="3"/>
     <col width="11" customWidth="1" style="3" min="4" max="4"/>
     <col width="11" customWidth="1" style="3" min="5" max="5"/>
@@ -1490,7 +1487,7 @@
           <t>I want (to go / going) home.</t>
         </is>
       </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>to go</t>
         </is>
@@ -1505,9 +1502,9 @@
         </is>
       </c>
       <c r="H2" s="18" t="n"/>
-      <c r="I2" s="20" t="n"/>
-      <c r="J2" s="20" t="n"/>
-      <c r="K2" s="20" t="n"/>
+      <c r="I2" s="19" t="n"/>
+      <c r="J2" s="19" t="n"/>
+      <c r="K2" s="19" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
@@ -1515,7 +1512,7 @@
           <t>바른 문장을 고르세요.</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1538,9 +1535,9 @@
         </is>
       </c>
       <c r="H3" s="18" t="n"/>
-      <c r="I3" s="20" t="n"/>
-      <c r="J3" s="20" t="n"/>
-      <c r="K3" s="20" t="n"/>
+      <c r="I3" s="19" t="n"/>
+      <c r="J3" s="19" t="n"/>
+      <c r="K3" s="19" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="18" t="inlineStr">
@@ -1549,7 +1546,7 @@
 Bag A is as heavy as Bag B.</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1560,9 +1557,9 @@
       <c r="F4" s="18" t="n"/>
       <c r="G4" s="18" t="n"/>
       <c r="H4" s="18" t="n"/>
-      <c r="I4" s="20" t="n"/>
-      <c r="J4" s="20" t="n"/>
-      <c r="K4" s="20" t="n"/>
+      <c r="I4" s="19" t="n"/>
+      <c r="J4" s="19" t="n"/>
+      <c r="K4" s="19" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -1570,7 +1567,7 @@
           <t>The clerk let me (try / to try) on the sneakers.</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>try</t>
         </is>
@@ -1595,7 +1592,7 @@
           <t>My dad made me (water / watering) the plants every morning.</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>water</t>
         </is>
@@ -1620,7 +1617,7 @@
           <t>The teacher had us (exchange / exchanged) our notebooks.</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
@@ -1645,7 +1642,7 @@
           <t>어법상 바른 문장을 고르세요.</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1678,7 +1675,7 @@
           <t>The flea market lets people (sell / to sell) their secondhand things.</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>sell</t>
         </is>
@@ -1703,7 +1700,7 @@
           <t>This wallet is as (cheap / cheaper) as that one.</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>cheap</t>
         </is>
@@ -1728,7 +1725,7 @@
           <t>어법상 바른 문장을 고르세요.</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1762,7 +1759,7 @@
 Mirror A is as expensive as Mirror B.</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -1791,7 +1788,7 @@
           <t>She sings as (beautiful / beautifully) as a singer.</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>beautifully</t>
         </is>
@@ -1835,7 +1832,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="3" min="1" max="1"/>
-    <col width="18" customWidth="1" style="3" min="2" max="2"/>
+    <col width="24" customWidth="1" style="3" min="2" max="2"/>
     <col width="14" customWidth="1" style="3" min="3" max="3"/>
     <col width="14" customWidth="1" style="3" min="4" max="4"/>
     <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="5" max="7"/>
@@ -1848,7 +1845,7 @@
           <t>문장</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>정답</t>
         </is>
@@ -1883,15 +1880,19 @@
       <c r="A2" s="18" t="inlineStr">
         <is>
           <t>그는 우유를 좋아하지 않는다.
-He [doesn't] like milk.</t>
-        </is>
-      </c>
-      <c r="B2" s="18" t="n"/>
+He ___ like milk.</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>doesn't</t>
+        </is>
+      </c>
       <c r="C2" s="18" t="n"/>
       <c r="D2" s="18" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="20" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
@@ -1910,17 +1911,21 @@
           <t>and로 한 문장을 만드세요.</t>
         </is>
       </c>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="20" t="n"/>
-      <c r="G3" s="20" t="n"/>
+      <c r="E3" s="19" t="n"/>
+      <c r="F3" s="19" t="n"/>
+      <c r="G3" s="19" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>My mom didn’t let me [stay out] late last night. (stay out)</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="n"/>
+          <t>My mom didn’t let me ___ late last night. (stay out)</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>stay out</t>
+        </is>
+      </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
           <t>let + 목적어 + 동사원형</t>
@@ -1938,10 +1943,14 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>The long line made the customers [wait] for an hour. (wait)</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="n"/>
+          <t>The long line made the customers ___ for an hour. (wait)</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
           <t>make + 목적어 + 동사원형</t>
@@ -1960,10 +1969,14 @@
       <c r="A6" s="14" t="inlineStr">
         <is>
           <t>그 점원은 내가 지갑을 교환하게 해 주었다.
-The clerk [let] me [exchange] the wallet.</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n"/>
+The clerk ___ me ___ the wallet.</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>let, exchange</t>
+        </is>
+      </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
           <t>let + 목적어 + 동사원형</t>
@@ -1982,10 +1995,14 @@
       <c r="A7" s="14" t="inlineStr">
         <is>
           <t>이 스카프는 저 모자만큼 비싸지 않다.
-This scarf is [not] [as|so] expensive [as] that cap.</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="n"/>
+This scarf is ___ ___ expensive ___ that cap.</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>not, as|so, as</t>
+        </is>
+      </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
           <t>not as(so) + 원급 + as: ~만큼 …하지 않다</t>
@@ -2029,10 +2046,14 @@
       <c r="A9" s="14" t="inlineStr">
         <is>
           <t>내 목도리는 네 재킷만큼 따뜻하다.
-My scarf is [as] warm [as] your jacket.</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="n"/>
+My scarf is ___ warm ___ your jacket.</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>as, as</t>
+        </is>
+      </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
           <t>as + 원급 + as: ~만큼 …한</t>
@@ -2068,14 +2089,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="3" min="1" max="1"/>
-    <col width="16" customWidth="1" style="3" min="2" max="2"/>
-    <col width="14" customWidth="1" style="3" min="3" max="3"/>
-    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="4" max="6"/>
-    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" style="3" min="2" max="2"/>
+    <col width="16" customWidth="1" style="3" min="3" max="3"/>
+    <col width="14" customWidth="1" style="3" min="4" max="4"/>
+    <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="5" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2084,27 +2106,32 @@
           <t>문장</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>해설</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>지시문</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>시간(초)</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -2113,65 +2140,80 @@
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>She [go → goes] to school every day.</t>
+          <t>She go to school every day.</t>
         </is>
       </c>
       <c r="B2" s="18" t="inlineStr">
         <is>
+          <t>go → goes</t>
+        </is>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
           <t>주어가 3인칭 단수면 동사에 -s</t>
         </is>
       </c>
-      <c r="C2" s="18" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>She had her son [to carry → carry] the boxes to the flea market.</t>
+          <t>She had her son to carry the boxes to the flea market.</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>to carry → carry</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
           <t>have + 목적어 + 동사원형 (to 없이)</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>어법상 틀린 부분을 찾아 바르게 고치세요.</t>
         </is>
       </c>
-      <c r="D3" s="17" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="17" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>He runs as [fastly → fast] as his brother.</t>
+          <t>He runs as fastly as his brother.</t>
         </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
+          <t>fastly → fast</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
           <t>fast는 부사도 fast (fastly는 없는 말)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>어법상 틀린 부분을 찾아 바르게 고치세요.</t>
         </is>
       </c>
-      <c r="D4" s="17" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="17" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
+    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="상태" error="사용, 검토, 보관 중에서 고르세요." type="list">
       <formula1>"사용,검토,보관"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="시간(초)" error="5~60 사이의 숫자를 쓰거나 비워 두세요." type="whole" operator="between">
       <formula1>5</formula1>
       <formula2>60</formula2>
     </dataValidation>
@@ -2190,8 +2232,8 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" style="3" min="1" max="1"/>
-    <col width="22" customWidth="1" style="3" min="2" max="2"/>
+    <col width="46" customWidth="1" style="3" min="1" max="1"/>
+    <col width="36" customWidth="1" style="3" min="2" max="2"/>
     <col width="14" customWidth="1" style="3" min="3" max="3"/>
     <col width="14" customWidth="1" style="3" min="4" max="4"/>
     <col hidden="1" outlineLevel="1" width="8" customWidth="1" style="9" min="5" max="7"/>
@@ -2201,12 +2243,12 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>정답 (조각을 / 로)</t>
+          <t>문장</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>우리말</t>
+          <t>정답</t>
         </is>
       </c>
       <c r="C1" s="11" t="inlineStr">
@@ -2235,32 +2277,34 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>my mom / makes / me / drink / milk / every day</t>
+          <t>엄마는 내가 매일 우유를 마시게 하신다.
+(drink / my mom / milk / every day / makes / me)</t>
         </is>
       </c>
       <c r="B2" s="18" t="inlineStr">
         <is>
-          <t>엄마는 내가 매일 우유를 마시게 하신다.</t>
+          <t>My mom makes me drink milk every day.</t>
         </is>
       </c>
       <c r="C2" s="18" t="n"/>
       <c r="D2" s="18" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="20" t="n"/>
-    </row>
-    <row r="3">
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>the clerk / let / me / try on / the scarf</t>
+          <t>점원은 내가 그 스카프를 착용해 보게 해 주었다.
+(let / me / the clerk / try on / the scarf)</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>점원은 내가 그 스카프를 착용해 보게 해 주었다.</t>
+          <t>The clerk let me try on the scarf.</t>
         </is>
       </c>
       <c r="C3" s="14" t="inlineStr">
@@ -2273,15 +2317,16 @@
       <c r="F3" s="16" t="n"/>
       <c r="G3" s="17" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>I / can / solve / the puzzle / as / easily / as / you</t>
+          <t>나는 너만큼 쉽게 그 퍼즐을 풀 수 있다.
+(as / easily / as / I / can / you / solve / the puzzle)</t>
         </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>나는 너만큼 쉽게 그 퍼즐을 풀 수 있다.</t>
+          <t>I can solve the puzzle as easily as you.</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -2294,15 +2339,16 @@
       <c r="F4" s="16" t="n"/>
       <c r="G4" s="17" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>these sneakers / are / not / as / expensive / as / those boots</t>
+          <t>이 운동화는 저 부츠만큼 비싸지 않다.
+(as / not / these sneakers / expensive / are / as / those boots)</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>이 운동화는 저 부츠만큼 비싸지 않다.</t>
+          <t>These sneakers are not as expensive as those boots.</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
